--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,11 +454,6 @@
           <t>ciudadanos_verificados</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PORC_AVANCE</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -480,10 +475,7 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12.98522007471171</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="3">
@@ -508,9 +500,6 @@
       <c r="E3" t="n">
         <v>14</v>
       </c>
-      <c r="F3" t="n">
-        <v>23.72881355932203</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,9 +523,6 @@
       <c r="E4" t="n">
         <v>39</v>
       </c>
-      <c r="F4" t="n">
-        <v>24.375</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,9 +546,6 @@
       <c r="E5" t="n">
         <v>163</v>
       </c>
-      <c r="F5" t="n">
-        <v>16.04330708661417</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,17 +560,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2484</v>
+        <v>5767</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.784219001610306</v>
+        <v>665</v>
       </c>
     </row>
     <row r="7">
@@ -603,17 +583,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
-      </c>
-      <c r="F7" t="n">
-        <v>9.725158562367865</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -624,48 +601,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECUAY</t>
+          <t>HUARI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>130</v>
+        <v>473</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
-      </c>
-      <c r="F8" t="n">
-        <v>26.15384615384616</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>RECUAY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -681,43 +652,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>473</v>
+        <v>175</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
-      </c>
-      <c r="F10" t="n">
-        <v>23.46723044397463</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REQUENA</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>392</v>
+        <v>473</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10.71428571428571</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -733,43 +698,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>627</v>
+        <v>392</v>
       </c>
       <c r="E12" t="n">
-        <v>236</v>
-      </c>
-      <c r="F12" t="n">
-        <v>37.63955342902711</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>REQUENA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1492</v>
+        <v>627</v>
       </c>
       <c r="E13" t="n">
-        <v>189</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12.66756032171582</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14">
@@ -780,48 +739,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7067</v>
+        <v>1492</v>
       </c>
       <c r="E14" t="n">
-        <v>648</v>
-      </c>
-      <c r="F14" t="n">
-        <v>9.169378802886657</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1401</v>
+        <v>7067</v>
       </c>
       <c r="E15" t="n">
-        <v>175</v>
-      </c>
-      <c r="F15" t="n">
-        <v>12.49107780157031</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16">
@@ -832,48 +785,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YAULI</t>
+          <t>SATIPO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>544</v>
+        <v>1401</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4.044117647058823</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>YAULI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5.152671755725191</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -889,95 +836,83 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>161</v>
+        <v>524</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5.590062111801243</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>807</v>
+        <v>161</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.230483271375465</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1051</v>
+        <v>807</v>
       </c>
       <c r="E20" t="n">
-        <v>121</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11.5128449096099</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LEONCIO PRADO</t>
+          <t>TARATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2404</v>
+        <v>515</v>
       </c>
       <c r="E21" t="n">
-        <v>301</v>
-      </c>
-      <c r="F21" t="n">
-        <v>12.52079866888519</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -988,22 +923,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MARAÑON</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>761</v>
+        <v>1051</v>
       </c>
       <c r="E22" t="n">
-        <v>123</v>
-      </c>
-      <c r="F22" t="n">
-        <v>16.16294349540079</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
@@ -1014,22 +946,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MARAÑON</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>841</v>
+        <v>2404</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.307966706302021</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24">
@@ -1040,22 +969,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YAROWILCA</t>
+          <t>MARAÑON</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1019</v>
+        <v>761</v>
       </c>
       <c r="E24" t="n">
-        <v>110</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10.79489695780177</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
@@ -1066,22 +992,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YAROWILCA</t>
+          <t>MARAÑON</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1251</v>
+        <v>841</v>
       </c>
       <c r="E25" t="n">
-        <v>119</v>
-      </c>
-      <c r="F25" t="n">
-        <v>9.512390087929656</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1097,147 +1020,129 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>728</v>
+        <v>1019</v>
       </c>
       <c r="E26" t="n">
-        <v>142</v>
-      </c>
-      <c r="F26" t="n">
-        <v>19.50549450549451</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>YAROWILCA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>525</v>
+        <v>1251</v>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
-      </c>
-      <c r="F27" t="n">
-        <v>15.42857142857143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>YAROWILCA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>236</v>
+        <v>728</v>
       </c>
       <c r="E28" t="n">
-        <v>26</v>
-      </c>
-      <c r="F28" t="n">
-        <v>11.01694915254237</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TOCACHE</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>734</v>
+        <v>525</v>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
-      </c>
-      <c r="F29" t="n">
-        <v>20.43596730245232</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E30" t="n">
-        <v>49</v>
-      </c>
-      <c r="F30" t="n">
-        <v>21.30434782608696</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TOCACHE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>246</v>
+        <v>734</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.439024390243902</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32">
@@ -1253,17 +1158,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="E32" t="n">
-        <v>24</v>
-      </c>
-      <c r="F32" t="n">
-        <v>32.43243243243244</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -1279,43 +1181,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
-      </c>
-      <c r="F33" t="n">
-        <v>9.444444444444445</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1902</v>
+        <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>202</v>
-      </c>
-      <c r="F34" t="n">
-        <v>10.62039957939012</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -1331,69 +1227,60 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
-      </c>
-      <c r="F35" t="n">
-        <v>17.42738589211618</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1075</v>
+        <v>1902</v>
       </c>
       <c r="E36" t="n">
-        <v>82</v>
-      </c>
-      <c r="F36" t="n">
-        <v>7.627906976744186</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>990</v>
+        <v>241</v>
       </c>
       <c r="E37" t="n">
-        <v>152</v>
-      </c>
-      <c r="F37" t="n">
-        <v>15.35353535353535</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
@@ -1409,17 +1296,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2150</v>
+        <v>1075</v>
       </c>
       <c r="E38" t="n">
-        <v>75</v>
-      </c>
-      <c r="F38" t="n">
-        <v>3.488372093023256</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
@@ -1430,256 +1314,295 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAMANA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1644</v>
+        <v>990</v>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.9732360097323601</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LUCANAS</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>695</v>
+        <v>2150</v>
       </c>
       <c r="E40" t="n">
-        <v>74</v>
-      </c>
-      <c r="F40" t="n">
-        <v>10.64748201438849</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAUCAR DEL SARA SARA</t>
+          <t>CAMANA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>355</v>
+        <v>1644</v>
       </c>
       <c r="E41" t="n">
-        <v>31</v>
-      </c>
-      <c r="F41" t="n">
-        <v>8.732394366197182</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>CARAVELI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E42" t="n">
-        <v>112</v>
-      </c>
-      <c r="F42" t="n">
-        <v>15.40577716643742</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>LUCANAS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1667</v>
+        <v>695</v>
       </c>
       <c r="E43" t="n">
-        <v>160</v>
-      </c>
-      <c r="F43" t="n">
-        <v>9.598080383923216</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANDIA</t>
+          <t>PAUCAR DEL SARA SARA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1350</v>
+        <v>355</v>
       </c>
       <c r="E44" t="n">
-        <v>139</v>
-      </c>
-      <c r="F44" t="n">
-        <v>10.2962962962963</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>VICTOR FAJARDO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1082</v>
+        <v>727</v>
       </c>
       <c r="E45" t="n">
-        <v>49</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4.528650646950092</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>320</v>
+        <v>1667</v>
       </c>
       <c r="E46" t="n">
-        <v>76</v>
-      </c>
-      <c r="F46" t="n">
-        <v>23.75</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>SANDIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>271</v>
+        <v>1350</v>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
-      </c>
-      <c r="F47" t="n">
-        <v>4.797047970479705</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E48" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>YAUYOS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HUANGASCAR</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>320</v>
+      </c>
+      <c r="E49" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>YAUYOS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AZANGARO</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>271</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>AMAZONAS</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>CHACHAPOYAS</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>SONCHE</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D51" t="n">
         <v>109</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E51" t="n">
         <v>19</v>
-      </c>
-      <c r="F48" t="n">
-        <v>17.43119266055046</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>ciudadanos_verificados</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PORC_AVANCE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -477,6 +482,9 @@
       <c r="E2" t="n">
         <v>1598</v>
       </c>
+      <c r="F2" t="n">
+        <v>12.97709923664122</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,6 +508,9 @@
       <c r="E3" t="n">
         <v>14</v>
       </c>
+      <c r="F3" t="n">
+        <v>23.72881355932203</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +534,9 @@
       <c r="E4" t="n">
         <v>39</v>
       </c>
+      <c r="F4" t="n">
+        <v>24.375</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +560,9 @@
       <c r="E5" t="n">
         <v>163</v>
       </c>
+      <c r="F5" t="n">
+        <v>16.04330708661417</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +586,9 @@
       <c r="E6" t="n">
         <v>665</v>
       </c>
+      <c r="F6" t="n">
+        <v>11.53112536847581</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -592,6 +612,9 @@
       <c r="E7" t="n">
         <v>93</v>
       </c>
+      <c r="F7" t="n">
+        <v>3.743961352657005</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +638,9 @@
       <c r="E8" t="n">
         <v>46</v>
       </c>
+      <c r="F8" t="n">
+        <v>9.725158562367865</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,6 +664,9 @@
       <c r="E9" t="n">
         <v>34</v>
       </c>
+      <c r="F9" t="n">
+        <v>26.15384615384616</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,6 +690,9 @@
       <c r="E10" t="n">
         <v>28</v>
       </c>
+      <c r="F10" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,6 +716,9 @@
       <c r="E11" t="n">
         <v>111</v>
       </c>
+      <c r="F11" t="n">
+        <v>23.46723044397463</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,6 +742,9 @@
       <c r="E12" t="n">
         <v>42</v>
       </c>
+      <c r="F12" t="n">
+        <v>10.71428571428571</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -730,6 +768,9 @@
       <c r="E13" t="n">
         <v>235</v>
       </c>
+      <c r="F13" t="n">
+        <v>37.48006379585327</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -753,6 +794,9 @@
       <c r="E14" t="n">
         <v>180</v>
       </c>
+      <c r="F14" t="n">
+        <v>12.06434316353887</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -776,6 +820,9 @@
       <c r="E15" t="n">
         <v>730</v>
       </c>
+      <c r="F15" t="n">
+        <v>10.32970142917787</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -799,6 +846,9 @@
       <c r="E16" t="n">
         <v>175</v>
       </c>
+      <c r="F16" t="n">
+        <v>12.49107780157031</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -822,6 +872,9 @@
       <c r="E17" t="n">
         <v>22</v>
       </c>
+      <c r="F17" t="n">
+        <v>4.044117647058823</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -845,6 +898,9 @@
       <c r="E18" t="n">
         <v>27</v>
       </c>
+      <c r="F18" t="n">
+        <v>5.152671755725191</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -868,6 +924,9 @@
       <c r="E19" t="n">
         <v>9</v>
       </c>
+      <c r="F19" t="n">
+        <v>5.590062111801243</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -891,6 +950,9 @@
       <c r="E20" t="n">
         <v>18</v>
       </c>
+      <c r="F20" t="n">
+        <v>2.230483271375465</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -914,6 +976,9 @@
       <c r="E21" t="n">
         <v>56</v>
       </c>
+      <c r="F21" t="n">
+        <v>10.87378640776699</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -937,6 +1002,9 @@
       <c r="E22" t="n">
         <v>121</v>
       </c>
+      <c r="F22" t="n">
+        <v>11.5128449096099</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -960,6 +1028,9 @@
       <c r="E23" t="n">
         <v>301</v>
       </c>
+      <c r="F23" t="n">
+        <v>12.52079866888519</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -983,6 +1054,9 @@
       <c r="E24" t="n">
         <v>123</v>
       </c>
+      <c r="F24" t="n">
+        <v>16.16294349540079</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1006,6 +1080,9 @@
       <c r="E25" t="n">
         <v>11</v>
       </c>
+      <c r="F25" t="n">
+        <v>1.307966706302021</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1029,6 +1106,9 @@
       <c r="E26" t="n">
         <v>109</v>
       </c>
+      <c r="F26" t="n">
+        <v>10.69676153091266</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1052,6 +1132,9 @@
       <c r="E27" t="n">
         <v>161</v>
       </c>
+      <c r="F27" t="n">
+        <v>12.86970423661071</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1075,6 +1158,9 @@
       <c r="E28" t="n">
         <v>142</v>
       </c>
+      <c r="F28" t="n">
+        <v>19.50549450549451</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1098,6 +1184,9 @@
       <c r="E29" t="n">
         <v>81</v>
       </c>
+      <c r="F29" t="n">
+        <v>15.42857142857143</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1121,6 +1210,9 @@
       <c r="E30" t="n">
         <v>26</v>
       </c>
+      <c r="F30" t="n">
+        <v>11.01694915254237</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1144,6 +1236,9 @@
       <c r="E31" t="n">
         <v>149</v>
       </c>
+      <c r="F31" t="n">
+        <v>20.29972752043597</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1167,6 +1262,9 @@
       <c r="E32" t="n">
         <v>35</v>
       </c>
+      <c r="F32" t="n">
+        <v>15.21739130434783</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1190,6 +1288,9 @@
       <c r="E33" t="n">
         <v>6</v>
       </c>
+      <c r="F33" t="n">
+        <v>2.439024390243902</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1213,6 +1314,9 @@
       <c r="E34" t="n">
         <v>24</v>
       </c>
+      <c r="F34" t="n">
+        <v>32.43243243243244</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1236,6 +1340,9 @@
       <c r="E35" t="n">
         <v>17</v>
       </c>
+      <c r="F35" t="n">
+        <v>9.444444444444445</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1259,6 +1366,9 @@
       <c r="E36" t="n">
         <v>202</v>
       </c>
+      <c r="F36" t="n">
+        <v>10.62039957939012</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1282,6 +1392,9 @@
       <c r="E37" t="n">
         <v>42</v>
       </c>
+      <c r="F37" t="n">
+        <v>17.42738589211618</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1305,6 +1418,9 @@
       <c r="E38" t="n">
         <v>81</v>
       </c>
+      <c r="F38" t="n">
+        <v>7.534883720930233</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1328,6 +1444,9 @@
       <c r="E39" t="n">
         <v>150</v>
       </c>
+      <c r="F39" t="n">
+        <v>15.15151515151515</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1351,6 +1470,9 @@
       <c r="E40" t="n">
         <v>73</v>
       </c>
+      <c r="F40" t="n">
+        <v>3.395348837209302</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1374,6 +1496,9 @@
       <c r="E41" t="n">
         <v>220</v>
       </c>
+      <c r="F41" t="n">
+        <v>13.38199513381995</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1397,6 +1522,9 @@
       <c r="E42" t="n">
         <v>100</v>
       </c>
+      <c r="F42" t="n">
+        <v>13.73626373626374</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1420,6 +1548,9 @@
       <c r="E43" t="n">
         <v>74</v>
       </c>
+      <c r="F43" t="n">
+        <v>10.64748201438849</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1443,6 +1574,9 @@
       <c r="E44" t="n">
         <v>31</v>
       </c>
+      <c r="F44" t="n">
+        <v>8.732394366197182</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1466,6 +1600,9 @@
       <c r="E45" t="n">
         <v>112</v>
       </c>
+      <c r="F45" t="n">
+        <v>15.40577716643742</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1489,6 +1626,9 @@
       <c r="E46" t="n">
         <v>160</v>
       </c>
+      <c r="F46" t="n">
+        <v>9.598080383923216</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1512,6 +1652,9 @@
       <c r="E47" t="n">
         <v>139</v>
       </c>
+      <c r="F47" t="n">
+        <v>10.2962962962963</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1535,6 +1678,9 @@
       <c r="E48" t="n">
         <v>49</v>
       </c>
+      <c r="F48" t="n">
+        <v>4.528650646950092</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1558,6 +1704,9 @@
       <c r="E49" t="n">
         <v>76</v>
       </c>
+      <c r="F49" t="n">
+        <v>23.75</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1581,6 +1730,9 @@
       <c r="E50" t="n">
         <v>13</v>
       </c>
+      <c r="F50" t="n">
+        <v>4.797047970479705</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1603,6 +1755,9 @@
       </c>
       <c r="E51" t="n">
         <v>19</v>
+      </c>
+      <c r="F51" t="n">
+        <v>17.43119266055046</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -480,10 +480,10 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>1598</v>
+        <v>3550</v>
       </c>
       <c r="F2" t="n">
-        <v>12.97709923664122</v>
+        <v>28.8289751502355</v>
       </c>
     </row>
     <row r="3">
@@ -506,10 +506,10 @@
         <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>23.72881355932203</v>
+        <v>25.42372881355932</v>
       </c>
     </row>
     <row r="4">
@@ -532,10 +532,10 @@
         <v>160</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>24.375</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="5">
@@ -558,10 +558,10 @@
         <v>1016</v>
       </c>
       <c r="E5" t="n">
-        <v>163</v>
+        <v>336</v>
       </c>
       <c r="F5" t="n">
-        <v>16.04330708661417</v>
+        <v>33.07086614173229</v>
       </c>
     </row>
     <row r="6">
@@ -584,10 +584,10 @@
         <v>5767</v>
       </c>
       <c r="E6" t="n">
-        <v>665</v>
+        <v>1420</v>
       </c>
       <c r="F6" t="n">
-        <v>11.53112536847581</v>
+        <v>24.62285417027917</v>
       </c>
     </row>
     <row r="7">
@@ -610,10 +610,10 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>324</v>
       </c>
       <c r="F7" t="n">
-        <v>3.743961352657005</v>
+        <v>13.04347826086956</v>
       </c>
     </row>
     <row r="8">
@@ -636,10 +636,10 @@
         <v>473</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>9.725158562367865</v>
+        <v>20.0845665961945</v>
       </c>
     </row>
     <row r="9">
@@ -662,10 +662,10 @@
         <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>26.15384615384616</v>
+        <v>35.38461538461539</v>
       </c>
     </row>
     <row r="10">
@@ -688,10 +688,10 @@
         <v>175</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>30.28571428571429</v>
       </c>
     </row>
     <row r="11">
@@ -714,10 +714,10 @@
         <v>473</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>235</v>
       </c>
       <c r="F11" t="n">
-        <v>23.46723044397463</v>
+        <v>49.68287526427061</v>
       </c>
     </row>
     <row r="12">
@@ -740,10 +740,10 @@
         <v>392</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>10.71428571428571</v>
+        <v>20.91836734693878</v>
       </c>
     </row>
     <row r="13">
@@ -766,10 +766,10 @@
         <v>627</v>
       </c>
       <c r="E13" t="n">
-        <v>235</v>
+        <v>329</v>
       </c>
       <c r="F13" t="n">
-        <v>37.48006379585327</v>
+        <v>52.47208931419458</v>
       </c>
     </row>
     <row r="14">
@@ -792,10 +792,10 @@
         <v>1492</v>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>417</v>
       </c>
       <c r="F14" t="n">
-        <v>12.06434316353887</v>
+        <v>27.94906166219839</v>
       </c>
     </row>
     <row r="15">
@@ -818,10 +818,10 @@
         <v>7067</v>
       </c>
       <c r="E15" t="n">
-        <v>730</v>
+        <v>1678</v>
       </c>
       <c r="F15" t="n">
-        <v>10.32970142917787</v>
+        <v>23.74416301117872</v>
       </c>
     </row>
     <row r="16">
@@ -844,10 +844,10 @@
         <v>1401</v>
       </c>
       <c r="E16" t="n">
-        <v>175</v>
+        <v>538</v>
       </c>
       <c r="F16" t="n">
-        <v>12.49107780157031</v>
+        <v>38.401142041399</v>
       </c>
     </row>
     <row r="17">
@@ -870,10 +870,10 @@
         <v>544</v>
       </c>
       <c r="E17" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>4.044117647058823</v>
+        <v>16.17647058823529</v>
       </c>
     </row>
     <row r="18">
@@ -896,10 +896,10 @@
         <v>524</v>
       </c>
       <c r="E18" t="n">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="F18" t="n">
-        <v>5.152671755725191</v>
+        <v>20.0381679389313</v>
       </c>
     </row>
     <row r="19">
@@ -922,10 +922,10 @@
         <v>161</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>5.590062111801243</v>
+        <v>11.80124223602484</v>
       </c>
     </row>
     <row r="20">
@@ -948,10 +948,10 @@
         <v>807</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>2.230483271375465</v>
+        <v>9.045848822800496</v>
       </c>
     </row>
     <row r="21">
@@ -974,10 +974,10 @@
         <v>515</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="F21" t="n">
-        <v>10.87378640776699</v>
+        <v>26.01941747572816</v>
       </c>
     </row>
     <row r="22">
@@ -1000,10 +1000,10 @@
         <v>1051</v>
       </c>
       <c r="E22" t="n">
-        <v>121</v>
+        <v>296</v>
       </c>
       <c r="F22" t="n">
-        <v>11.5128449096099</v>
+        <v>28.16365366317793</v>
       </c>
     </row>
     <row r="23">
@@ -1026,10 +1026,10 @@
         <v>2404</v>
       </c>
       <c r="E23" t="n">
-        <v>301</v>
+        <v>856</v>
       </c>
       <c r="F23" t="n">
-        <v>12.52079866888519</v>
+        <v>35.60732113144759</v>
       </c>
     </row>
     <row r="24">
@@ -1052,10 +1052,10 @@
         <v>761</v>
       </c>
       <c r="E24" t="n">
-        <v>123</v>
+        <v>263</v>
       </c>
       <c r="F24" t="n">
-        <v>16.16294349540079</v>
+        <v>34.55978975032852</v>
       </c>
     </row>
     <row r="25">
@@ -1078,10 +1078,10 @@
         <v>841</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>1.307966706302021</v>
+        <v>3.56718192627824</v>
       </c>
     </row>
     <row r="26">
@@ -1104,10 +1104,10 @@
         <v>1019</v>
       </c>
       <c r="E26" t="n">
-        <v>109</v>
+        <v>221</v>
       </c>
       <c r="F26" t="n">
-        <v>10.69676153091266</v>
+        <v>21.68792934249264</v>
       </c>
     </row>
     <row r="27">
@@ -1130,10 +1130,10 @@
         <v>1251</v>
       </c>
       <c r="E27" t="n">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="F27" t="n">
-        <v>12.86970423661071</v>
+        <v>19.50439648281375</v>
       </c>
     </row>
     <row r="28">
@@ -1156,10 +1156,10 @@
         <v>728</v>
       </c>
       <c r="E28" t="n">
-        <v>142</v>
+        <v>273</v>
       </c>
       <c r="F28" t="n">
-        <v>19.50549450549451</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="29">
@@ -1182,10 +1182,10 @@
         <v>525</v>
       </c>
       <c r="E29" t="n">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="F29" t="n">
-        <v>15.42857142857143</v>
+        <v>49.71428571428572</v>
       </c>
     </row>
     <row r="30">
@@ -1208,10 +1208,10 @@
         <v>236</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F30" t="n">
-        <v>11.01694915254237</v>
+        <v>23.30508474576271</v>
       </c>
     </row>
     <row r="31">
@@ -1234,10 +1234,10 @@
         <v>734</v>
       </c>
       <c r="E31" t="n">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="F31" t="n">
-        <v>20.29972752043597</v>
+        <v>39.6457765667575</v>
       </c>
     </row>
     <row r="32">
@@ -1260,10 +1260,10 @@
         <v>230</v>
       </c>
       <c r="E32" t="n">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="F32" t="n">
-        <v>15.21739130434783</v>
+        <v>74.78260869565217</v>
       </c>
     </row>
     <row r="33">
@@ -1286,10 +1286,10 @@
         <v>246</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="F33" t="n">
-        <v>2.439024390243902</v>
+        <v>31.30081300813008</v>
       </c>
     </row>
     <row r="34">
@@ -1312,10 +1312,10 @@
         <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>32.43243243243244</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="35">
@@ -1338,10 +1338,10 @@
         <v>180</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F35" t="n">
-        <v>9.444444444444445</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -1364,10 +1364,10 @@
         <v>1902</v>
       </c>
       <c r="E36" t="n">
-        <v>202</v>
+        <v>574</v>
       </c>
       <c r="F36" t="n">
-        <v>10.62039957939012</v>
+        <v>30.17875920084122</v>
       </c>
     </row>
     <row r="37">
@@ -1390,10 +1390,10 @@
         <v>241</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="F37" t="n">
-        <v>17.42738589211618</v>
+        <v>36.92946058091287</v>
       </c>
     </row>
     <row r="38">
@@ -1416,10 +1416,10 @@
         <v>1075</v>
       </c>
       <c r="E38" t="n">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="F38" t="n">
-        <v>7.534883720930233</v>
+        <v>18.13953488372093</v>
       </c>
     </row>
     <row r="39">
@@ -1442,10 +1442,10 @@
         <v>990</v>
       </c>
       <c r="E39" t="n">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="F39" t="n">
-        <v>15.15151515151515</v>
+        <v>39.39393939393939</v>
       </c>
     </row>
     <row r="40">
@@ -1468,10 +1468,10 @@
         <v>2150</v>
       </c>
       <c r="E40" t="n">
-        <v>73</v>
+        <v>212</v>
       </c>
       <c r="F40" t="n">
-        <v>3.395348837209302</v>
+        <v>9.86046511627907</v>
       </c>
     </row>
     <row r="41">
@@ -1494,10 +1494,10 @@
         <v>1644</v>
       </c>
       <c r="E41" t="n">
-        <v>220</v>
+        <v>399</v>
       </c>
       <c r="F41" t="n">
-        <v>13.38199513381995</v>
+        <v>24.27007299270073</v>
       </c>
     </row>
     <row r="42">
@@ -1520,10 +1520,10 @@
         <v>728</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="F42" t="n">
-        <v>13.73626373626374</v>
+        <v>23.76373626373626</v>
       </c>
     </row>
     <row r="43">
@@ -1546,10 +1546,10 @@
         <v>695</v>
       </c>
       <c r="E43" t="n">
-        <v>74</v>
+        <v>222</v>
       </c>
       <c r="F43" t="n">
-        <v>10.64748201438849</v>
+        <v>31.94244604316547</v>
       </c>
     </row>
     <row r="44">
@@ -1572,10 +1572,10 @@
         <v>355</v>
       </c>
       <c r="E44" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="F44" t="n">
-        <v>8.732394366197182</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -1598,10 +1598,10 @@
         <v>727</v>
       </c>
       <c r="E45" t="n">
-        <v>112</v>
+        <v>341</v>
       </c>
       <c r="F45" t="n">
-        <v>15.40577716643742</v>
+        <v>46.9050894085282</v>
       </c>
     </row>
     <row r="46">
@@ -1624,10 +1624,10 @@
         <v>1667</v>
       </c>
       <c r="E46" t="n">
-        <v>160</v>
+        <v>569</v>
       </c>
       <c r="F46" t="n">
-        <v>9.598080383923216</v>
+        <v>34.13317336532693</v>
       </c>
     </row>
     <row r="47">
@@ -1650,10 +1650,10 @@
         <v>1350</v>
       </c>
       <c r="E47" t="n">
-        <v>139</v>
+        <v>344</v>
       </c>
       <c r="F47" t="n">
-        <v>10.2962962962963</v>
+        <v>25.48148148148148</v>
       </c>
     </row>
     <row r="48">
@@ -1676,10 +1676,10 @@
         <v>1082</v>
       </c>
       <c r="E48" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F48" t="n">
-        <v>4.528650646950092</v>
+        <v>6.746765249537892</v>
       </c>
     </row>
     <row r="49">
@@ -1702,10 +1702,10 @@
         <v>320</v>
       </c>
       <c r="E49" t="n">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="F49" t="n">
-        <v>23.75</v>
+        <v>74.0625</v>
       </c>
     </row>
     <row r="50">
@@ -1728,10 +1728,10 @@
         <v>271</v>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>4.797047970479705</v>
+        <v>16.97416974169742</v>
       </c>
     </row>
     <row r="51">
@@ -1754,10 +1754,10 @@
         <v>109</v>
       </c>
       <c r="E51" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F51" t="n">
-        <v>17.43119266055046</v>
+        <v>39.44954128440367</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,21 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>PORC_AVANCE</t>
         </is>
       </c>
@@ -483,6 +498,15 @@
         <v>3550</v>
       </c>
       <c r="F2" t="n">
+        <v>812</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2540</v>
+      </c>
+      <c r="H2" t="n">
+        <v>189</v>
+      </c>
+      <c r="I2" t="n">
         <v>28.8289751502355</v>
       </c>
     </row>
@@ -509,6 +533,15 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>25.42372881355932</v>
       </c>
     </row>
@@ -535,6 +568,15 @@
         <v>55</v>
       </c>
       <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
         <v>34.375</v>
       </c>
     </row>
@@ -561,6 +603,15 @@
         <v>336</v>
       </c>
       <c r="F5" t="n">
+        <v>115</v>
+      </c>
+      <c r="G5" t="n">
+        <v>220</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>33.07086614173229</v>
       </c>
     </row>
@@ -587,6 +638,15 @@
         <v>1420</v>
       </c>
       <c r="F6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G6" t="n">
+        <v>826</v>
+      </c>
+      <c r="H6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" t="n">
         <v>24.62285417027917</v>
       </c>
     </row>
@@ -613,6 +673,15 @@
         <v>324</v>
       </c>
       <c r="F7" t="n">
+        <v>161</v>
+      </c>
+      <c r="G7" t="n">
+        <v>154</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
         <v>13.04347826086956</v>
       </c>
     </row>
@@ -639,6 +708,15 @@
         <v>95</v>
       </c>
       <c r="F8" t="n">
+        <v>49</v>
+      </c>
+      <c r="G8" t="n">
+        <v>44</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
         <v>20.0845665961945</v>
       </c>
     </row>
@@ -665,6 +743,15 @@
         <v>46</v>
       </c>
       <c r="F9" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>35.38461538461539</v>
       </c>
     </row>
@@ -691,6 +778,15 @@
         <v>53</v>
       </c>
       <c r="F10" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>30.28571428571429</v>
       </c>
     </row>
@@ -717,6 +813,15 @@
         <v>235</v>
       </c>
       <c r="F11" t="n">
+        <v>171</v>
+      </c>
+      <c r="G11" t="n">
+        <v>63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
         <v>49.68287526427061</v>
       </c>
     </row>
@@ -743,6 +848,15 @@
         <v>82</v>
       </c>
       <c r="F12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>65</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>20.91836734693878</v>
       </c>
     </row>
@@ -769,6 +883,15 @@
         <v>329</v>
       </c>
       <c r="F13" t="n">
+        <v>64</v>
+      </c>
+      <c r="G13" t="n">
+        <v>265</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>52.47208931419458</v>
       </c>
     </row>
@@ -795,6 +918,15 @@
         <v>417</v>
       </c>
       <c r="F14" t="n">
+        <v>249</v>
+      </c>
+      <c r="G14" t="n">
+        <v>141</v>
+      </c>
+      <c r="H14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" t="n">
         <v>27.94906166219839</v>
       </c>
     </row>
@@ -821,6 +953,15 @@
         <v>1678</v>
       </c>
       <c r="F15" t="n">
+        <v>907</v>
+      </c>
+      <c r="G15" t="n">
+        <v>476</v>
+      </c>
+      <c r="H15" t="n">
+        <v>298</v>
+      </c>
+      <c r="I15" t="n">
         <v>23.74416301117872</v>
       </c>
     </row>
@@ -847,6 +988,15 @@
         <v>538</v>
       </c>
       <c r="F16" t="n">
+        <v>413</v>
+      </c>
+      <c r="G16" t="n">
+        <v>125</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>38.401142041399</v>
       </c>
     </row>
@@ -873,6 +1023,15 @@
         <v>88</v>
       </c>
       <c r="F17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" t="n">
         <v>16.17647058823529</v>
       </c>
     </row>
@@ -899,6 +1058,15 @@
         <v>105</v>
       </c>
       <c r="F18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" t="n">
+        <v>45</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>20.0381679389313</v>
       </c>
     </row>
@@ -925,6 +1093,15 @@
         <v>19</v>
       </c>
       <c r="F19" t="n">
+        <v>18</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>11.80124223602484</v>
       </c>
     </row>
@@ -951,6 +1128,15 @@
         <v>73</v>
       </c>
       <c r="F20" t="n">
+        <v>58</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
         <v>9.045848822800496</v>
       </c>
     </row>
@@ -977,6 +1163,15 @@
         <v>134</v>
       </c>
       <c r="F21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G21" t="n">
+        <v>77</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="n">
         <v>26.01941747572816</v>
       </c>
     </row>
@@ -1003,6 +1198,15 @@
         <v>296</v>
       </c>
       <c r="F22" t="n">
+        <v>108</v>
+      </c>
+      <c r="G22" t="n">
+        <v>169</v>
+      </c>
+      <c r="H22" t="n">
+        <v>19</v>
+      </c>
+      <c r="I22" t="n">
         <v>28.16365366317793</v>
       </c>
     </row>
@@ -1029,6 +1233,15 @@
         <v>856</v>
       </c>
       <c r="F23" t="n">
+        <v>625</v>
+      </c>
+      <c r="G23" t="n">
+        <v>217</v>
+      </c>
+      <c r="H23" t="n">
+        <v>13</v>
+      </c>
+      <c r="I23" t="n">
         <v>35.60732113144759</v>
       </c>
     </row>
@@ -1055,6 +1268,15 @@
         <v>263</v>
       </c>
       <c r="F24" t="n">
+        <v>223</v>
+      </c>
+      <c r="G24" t="n">
+        <v>39</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
         <v>34.55978975032852</v>
       </c>
     </row>
@@ -1081,6 +1303,15 @@
         <v>30</v>
       </c>
       <c r="F25" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>3.56718192627824</v>
       </c>
     </row>
@@ -1107,6 +1338,15 @@
         <v>221</v>
       </c>
       <c r="F26" t="n">
+        <v>57</v>
+      </c>
+      <c r="G26" t="n">
+        <v>159</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="n">
         <v>21.68792934249264</v>
       </c>
     </row>
@@ -1133,6 +1373,15 @@
         <v>244</v>
       </c>
       <c r="F27" t="n">
+        <v>82</v>
+      </c>
+      <c r="G27" t="n">
+        <v>162</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>19.50439648281375</v>
       </c>
     </row>
@@ -1159,6 +1408,15 @@
         <v>273</v>
       </c>
       <c r="F28" t="n">
+        <v>105</v>
+      </c>
+      <c r="G28" t="n">
+        <v>161</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -1185,6 +1443,15 @@
         <v>261</v>
       </c>
       <c r="F29" t="n">
+        <v>132</v>
+      </c>
+      <c r="G29" t="n">
+        <v>119</v>
+      </c>
+      <c r="H29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" t="n">
         <v>49.71428571428572</v>
       </c>
     </row>
@@ -1211,6 +1478,15 @@
         <v>55</v>
       </c>
       <c r="F30" t="n">
+        <v>46</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
         <v>23.30508474576271</v>
       </c>
     </row>
@@ -1237,6 +1513,15 @@
         <v>291</v>
       </c>
       <c r="F31" t="n">
+        <v>86</v>
+      </c>
+      <c r="G31" t="n">
+        <v>205</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>39.6457765667575</v>
       </c>
     </row>
@@ -1263,6 +1548,15 @@
         <v>172</v>
       </c>
       <c r="F32" t="n">
+        <v>98</v>
+      </c>
+      <c r="G32" t="n">
+        <v>72</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
         <v>74.78260869565217</v>
       </c>
     </row>
@@ -1289,6 +1583,15 @@
         <v>77</v>
       </c>
       <c r="F33" t="n">
+        <v>70</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
         <v>31.30081300813008</v>
       </c>
     </row>
@@ -1315,6 +1618,15 @@
         <v>54</v>
       </c>
       <c r="F34" t="n">
+        <v>38</v>
+      </c>
+      <c r="G34" t="n">
+        <v>16</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -1341,6 +1653,15 @@
         <v>45</v>
       </c>
       <c r="F35" t="n">
+        <v>26</v>
+      </c>
+      <c r="G35" t="n">
+        <v>19</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1367,6 +1688,15 @@
         <v>574</v>
       </c>
       <c r="F36" t="n">
+        <v>139</v>
+      </c>
+      <c r="G36" t="n">
+        <v>424</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="n">
         <v>30.17875920084122</v>
       </c>
     </row>
@@ -1393,6 +1723,15 @@
         <v>89</v>
       </c>
       <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>88</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>36.92946058091287</v>
       </c>
     </row>
@@ -1419,6 +1758,15 @@
         <v>195</v>
       </c>
       <c r="F38" t="n">
+        <v>146</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34</v>
+      </c>
+      <c r="H38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I38" t="n">
         <v>18.13953488372093</v>
       </c>
     </row>
@@ -1445,6 +1793,15 @@
         <v>390</v>
       </c>
       <c r="F39" t="n">
+        <v>255</v>
+      </c>
+      <c r="G39" t="n">
+        <v>119</v>
+      </c>
+      <c r="H39" t="n">
+        <v>16</v>
+      </c>
+      <c r="I39" t="n">
         <v>39.39393939393939</v>
       </c>
     </row>
@@ -1471,6 +1828,15 @@
         <v>212</v>
       </c>
       <c r="F40" t="n">
+        <v>111</v>
+      </c>
+      <c r="G40" t="n">
+        <v>92</v>
+      </c>
+      <c r="H40" t="n">
+        <v>9</v>
+      </c>
+      <c r="I40" t="n">
         <v>9.86046511627907</v>
       </c>
     </row>
@@ -1497,6 +1863,15 @@
         <v>399</v>
       </c>
       <c r="F41" t="n">
+        <v>275</v>
+      </c>
+      <c r="G41" t="n">
+        <v>79</v>
+      </c>
+      <c r="H41" t="n">
+        <v>44</v>
+      </c>
+      <c r="I41" t="n">
         <v>24.27007299270073</v>
       </c>
     </row>
@@ -1523,6 +1898,15 @@
         <v>173</v>
       </c>
       <c r="F42" t="n">
+        <v>127</v>
+      </c>
+      <c r="G42" t="n">
+        <v>42</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" t="n">
         <v>23.76373626373626</v>
       </c>
     </row>
@@ -1549,6 +1933,15 @@
         <v>222</v>
       </c>
       <c r="F43" t="n">
+        <v>124</v>
+      </c>
+      <c r="G43" t="n">
+        <v>96</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
         <v>31.94244604316547</v>
       </c>
     </row>
@@ -1575,6 +1968,15 @@
         <v>142</v>
       </c>
       <c r="F44" t="n">
+        <v>99</v>
+      </c>
+      <c r="G44" t="n">
+        <v>43</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1601,6 +2003,15 @@
         <v>341</v>
       </c>
       <c r="F45" t="n">
+        <v>91</v>
+      </c>
+      <c r="G45" t="n">
+        <v>248</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>46.9050894085282</v>
       </c>
     </row>
@@ -1627,6 +2038,15 @@
         <v>569</v>
       </c>
       <c r="F46" t="n">
+        <v>346</v>
+      </c>
+      <c r="G46" t="n">
+        <v>90</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
         <v>34.13317336532693</v>
       </c>
     </row>
@@ -1653,6 +2073,15 @@
         <v>344</v>
       </c>
       <c r="F47" t="n">
+        <v>172</v>
+      </c>
+      <c r="G47" t="n">
+        <v>125</v>
+      </c>
+      <c r="H47" t="n">
+        <v>45</v>
+      </c>
+      <c r="I47" t="n">
         <v>25.48148148148148</v>
       </c>
     </row>
@@ -1679,6 +2108,15 @@
         <v>73</v>
       </c>
       <c r="F48" t="n">
+        <v>64</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>6.746765249537892</v>
       </c>
     </row>
@@ -1705,6 +2143,15 @@
         <v>237</v>
       </c>
       <c r="F49" t="n">
+        <v>134</v>
+      </c>
+      <c r="G49" t="n">
+        <v>103</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>74.0625</v>
       </c>
     </row>
@@ -1731,6 +2178,15 @@
         <v>46</v>
       </c>
       <c r="F50" t="n">
+        <v>17</v>
+      </c>
+      <c r="G50" t="n">
+        <v>29</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>16.97416974169742</v>
       </c>
     </row>
@@ -1757,6 +2213,15 @@
         <v>43</v>
       </c>
       <c r="F51" t="n">
+        <v>13</v>
+      </c>
+      <c r="G51" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>39.44954128440367</v>
       </c>
     </row>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,19 +495,19 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>3550</v>
+        <v>6761</v>
       </c>
       <c r="F2" t="n">
-        <v>812</v>
+        <v>1818</v>
       </c>
       <c r="G2" t="n">
-        <v>2540</v>
+        <v>4691</v>
       </c>
       <c r="H2" t="n">
-        <v>189</v>
+        <v>245</v>
       </c>
       <c r="I2" t="n">
-        <v>28.8289751502355</v>
+        <v>54.90498619457528</v>
       </c>
     </row>
     <row r="3">
@@ -530,19 +530,19 @@
         <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>25.42372881355932</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>160</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="I4" t="n">
-        <v>34.375</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="5">
@@ -600,19 +600,19 @@
         <v>1016</v>
       </c>
       <c r="E5" t="n">
-        <v>336</v>
+        <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>383</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>33.07086614173229</v>
+        <v>59.05511811023622</v>
       </c>
     </row>
     <row r="6">
@@ -635,19 +635,19 @@
         <v>5767</v>
       </c>
       <c r="E6" t="n">
-        <v>1420</v>
+        <v>4193</v>
       </c>
       <c r="F6" t="n">
-        <v>550</v>
+        <v>1230</v>
       </c>
       <c r="G6" t="n">
-        <v>826</v>
+        <v>2885</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I6" t="n">
-        <v>24.62285417027917</v>
+        <v>72.7067799549159</v>
       </c>
     </row>
     <row r="7">
@@ -670,19 +670,19 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>324</v>
+        <v>613</v>
       </c>
       <c r="F7" t="n">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="G7" t="n">
-        <v>154</v>
+        <v>367</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>13.04347826086956</v>
+        <v>24.67793880837359</v>
       </c>
     </row>
     <row r="8">
@@ -705,19 +705,19 @@
         <v>473</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>20.0845665961945</v>
+        <v>24.52431289640592</v>
       </c>
     </row>
     <row r="9">
@@ -740,19 +740,19 @@
         <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>35.38461538461539</v>
+        <v>74.61538461538461</v>
       </c>
     </row>
     <row r="10">
@@ -763,31 +763,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>401</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>30.28571428571429</v>
+        <v>29.42643391521197</v>
       </c>
     </row>
     <row r="11">
@@ -803,61 +803,61 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>473</v>
+        <v>175</v>
       </c>
       <c r="E11" t="n">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="F11" t="n">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>49.68287526427061</v>
+        <v>66.28571428571428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>REQUENA</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>392</v>
+        <v>473</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>20.91836734693878</v>
+        <v>79.70401691331924</v>
       </c>
     </row>
     <row r="13">
@@ -873,61 +873,61 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>627</v>
+        <v>392</v>
       </c>
       <c r="E13" t="n">
-        <v>329</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>265</v>
+        <v>68</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>52.47208931419458</v>
+        <v>22.19387755102041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>REQUENA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1492</v>
+        <v>627</v>
       </c>
       <c r="E14" t="n">
-        <v>417</v>
+        <v>361</v>
       </c>
       <c r="F14" t="n">
-        <v>249</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>141</v>
+        <v>295</v>
       </c>
       <c r="H14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>27.94906166219839</v>
+        <v>57.57575757575758</v>
       </c>
     </row>
     <row r="15">
@@ -938,66 +938,66 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7067</v>
+        <v>1492</v>
       </c>
       <c r="E15" t="n">
-        <v>1678</v>
+        <v>805</v>
       </c>
       <c r="F15" t="n">
-        <v>907</v>
+        <v>535</v>
       </c>
       <c r="G15" t="n">
-        <v>476</v>
+        <v>198</v>
       </c>
       <c r="H15" t="n">
-        <v>298</v>
+        <v>69</v>
       </c>
       <c r="I15" t="n">
-        <v>23.74416301117872</v>
+        <v>53.95442359249329</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1401</v>
+        <v>7067</v>
       </c>
       <c r="E16" t="n">
-        <v>538</v>
+        <v>3099</v>
       </c>
       <c r="F16" t="n">
-        <v>413</v>
+        <v>1571</v>
       </c>
       <c r="G16" t="n">
-        <v>125</v>
+        <v>785</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="I16" t="n">
-        <v>38.401142041399</v>
+        <v>43.85170510824961</v>
       </c>
     </row>
     <row r="17">
@@ -1008,66 +1008,66 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YAULI</t>
+          <t>SATIPO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>544</v>
+        <v>1401</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>617</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>481</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>16.17647058823529</v>
+        <v>44.03997144896503</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>YAULI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="E18" t="n">
-        <v>105</v>
+        <v>350</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="I18" t="n">
-        <v>20.0381679389313</v>
+        <v>64.33823529411765</v>
       </c>
     </row>
     <row r="19">
@@ -1083,131 +1083,131 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>161</v>
+        <v>524</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>11.80124223602484</v>
+        <v>42.36641221374045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>807</v>
+        <v>161</v>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>9.045848822800496</v>
+        <v>31.67701863354037</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TARATA</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>515</v>
+        <v>807</v>
       </c>
       <c r="E21" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="G21" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>26.01941747572816</v>
+        <v>21.8091697645601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TARATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1051</v>
+        <v>515</v>
       </c>
       <c r="E22" t="n">
-        <v>296</v>
+        <v>243</v>
       </c>
       <c r="F22" t="n">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="G22" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I22" t="n">
-        <v>28.16365366317793</v>
+        <v>47.18446601941748</v>
       </c>
     </row>
     <row r="23">
@@ -1218,31 +1218,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LEONCIO PRADO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2404</v>
+        <v>1051</v>
       </c>
       <c r="E23" t="n">
-        <v>856</v>
+        <v>528</v>
       </c>
       <c r="F23" t="n">
-        <v>625</v>
+        <v>203</v>
       </c>
       <c r="G23" t="n">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="H23" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I23" t="n">
-        <v>35.60732113144759</v>
+        <v>50.23786869647955</v>
       </c>
     </row>
     <row r="24">
@@ -1253,31 +1253,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MARAÑON</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>761</v>
+        <v>2404</v>
       </c>
       <c r="E24" t="n">
-        <v>263</v>
+        <v>1777</v>
       </c>
       <c r="F24" t="n">
-        <v>223</v>
+        <v>1325</v>
       </c>
       <c r="G24" t="n">
-        <v>39</v>
+        <v>418</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I24" t="n">
-        <v>34.55978975032852</v>
+        <v>73.91846921797006</v>
       </c>
     </row>
     <row r="25">
@@ -1293,26 +1293,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>841</v>
+        <v>761</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>453</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>393</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>3.56718192627824</v>
+        <v>59.526938239159</v>
       </c>
     </row>
     <row r="26">
@@ -1323,31 +1323,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YAROWILCA</t>
+          <t>MARAÑON</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1019</v>
+        <v>841</v>
       </c>
       <c r="E26" t="n">
-        <v>221</v>
+        <v>123</v>
       </c>
       <c r="F26" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G26" t="n">
-        <v>159</v>
+        <v>34</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>21.68792934249264</v>
+        <v>14.62544589774079</v>
       </c>
     </row>
     <row r="27">
@@ -1363,26 +1363,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1251</v>
+        <v>1019</v>
       </c>
       <c r="E27" t="n">
-        <v>244</v>
+        <v>377</v>
       </c>
       <c r="F27" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G27" t="n">
-        <v>162</v>
+        <v>296</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>19.50439648281375</v>
+        <v>36.99705593719333</v>
       </c>
     </row>
     <row r="28">
@@ -1398,61 +1398,61 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>728</v>
+        <v>1251</v>
       </c>
       <c r="E28" t="n">
-        <v>273</v>
+        <v>576</v>
       </c>
       <c r="F28" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="G28" t="n">
-        <v>161</v>
+        <v>439</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>37.5</v>
+        <v>46.0431654676259</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>YAROWILCA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>525</v>
+        <v>728</v>
       </c>
       <c r="E29" t="n">
-        <v>261</v>
+        <v>491</v>
       </c>
       <c r="F29" t="n">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="G29" t="n">
-        <v>119</v>
+        <v>215</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>49.71428571428572</v>
+        <v>67.44505494505495</v>
       </c>
     </row>
     <row r="30">
@@ -1468,96 +1468,96 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>236</v>
+        <v>525</v>
       </c>
       <c r="E30" t="n">
-        <v>55</v>
+        <v>445</v>
       </c>
       <c r="F30" t="n">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>194</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
-        <v>23.30508474576271</v>
+        <v>84.76190476190476</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TOCACHE</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>734</v>
+        <v>236</v>
       </c>
       <c r="E31" t="n">
-        <v>291</v>
+        <v>146</v>
       </c>
       <c r="F31" t="n">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="G31" t="n">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>39.6457765667575</v>
+        <v>61.86440677966102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TOCACHE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>230</v>
+        <v>734</v>
       </c>
       <c r="E32" t="n">
-        <v>172</v>
+        <v>447</v>
       </c>
       <c r="F32" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="G32" t="n">
-        <v>72</v>
+        <v>298</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>74.78260869565217</v>
+        <v>60.89918256130791</v>
       </c>
     </row>
     <row r="33">
@@ -1573,26 +1573,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="E33" t="n">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="F33" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>31.30081300813008</v>
+        <v>74.78260869565217</v>
       </c>
     </row>
     <row r="34">
@@ -1608,26 +1608,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="G34" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>72.97297297297297</v>
+        <v>54.87804878048781</v>
       </c>
     </row>
     <row r="35">
@@ -1643,131 +1643,131 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="E35" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F35" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1902</v>
+        <v>180</v>
       </c>
       <c r="E36" t="n">
-        <v>574</v>
+        <v>45</v>
       </c>
       <c r="F36" t="n">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>424</v>
+        <v>19</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>30.17875920084122</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>241</v>
+        <v>1902</v>
       </c>
       <c r="E37" t="n">
-        <v>89</v>
+        <v>1002</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="G37" t="n">
-        <v>88</v>
+        <v>731</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I37" t="n">
-        <v>36.92946058091287</v>
+        <v>52.6813880126183</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1075</v>
+        <v>241</v>
       </c>
       <c r="E38" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F38" t="n">
-        <v>146</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>18.13953488372093</v>
+        <v>64.31535269709543</v>
       </c>
     </row>
     <row r="39">
@@ -1783,26 +1783,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>990</v>
+        <v>1075</v>
       </c>
       <c r="E39" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="F39" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="G39" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H39" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I39" t="n">
-        <v>39.39393939393939</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -1818,26 +1818,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2150</v>
+        <v>990</v>
       </c>
       <c r="E40" t="n">
-        <v>212</v>
+        <v>746</v>
       </c>
       <c r="F40" t="n">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="G40" t="n">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I40" t="n">
-        <v>9.86046511627907</v>
+        <v>75.35353535353535</v>
       </c>
     </row>
     <row r="41">
@@ -1848,31 +1848,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAMANA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1644</v>
+        <v>2150</v>
       </c>
       <c r="E41" t="n">
-        <v>399</v>
+        <v>693</v>
       </c>
       <c r="F41" t="n">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="G41" t="n">
-        <v>79</v>
+        <v>434</v>
       </c>
       <c r="H41" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>24.27007299270073</v>
+        <v>32.23255813953488</v>
       </c>
     </row>
     <row r="42">
@@ -1883,66 +1883,66 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CARAVELI</t>
+          <t>CAMANA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>728</v>
+        <v>1644</v>
       </c>
       <c r="E42" t="n">
-        <v>173</v>
+        <v>930</v>
       </c>
       <c r="F42" t="n">
-        <v>127</v>
+        <v>582</v>
       </c>
       <c r="G42" t="n">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>208</v>
       </c>
       <c r="I42" t="n">
-        <v>23.76373626373626</v>
+        <v>56.56934306569343</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LUCANAS</t>
+          <t>CARAVELI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>695</v>
+        <v>728</v>
       </c>
       <c r="E43" t="n">
-        <v>222</v>
+        <v>486</v>
       </c>
       <c r="F43" t="n">
-        <v>124</v>
+        <v>392</v>
       </c>
       <c r="G43" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>31.94244604316547</v>
+        <v>66.75824175824175</v>
       </c>
     </row>
     <row r="44">
@@ -1953,31 +1953,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PAUCAR DEL SARA SARA</t>
+          <t>LUCANAS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>355</v>
+        <v>695</v>
       </c>
       <c r="E44" t="n">
-        <v>142</v>
+        <v>368</v>
       </c>
       <c r="F44" t="n">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="G44" t="n">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I44" t="n">
-        <v>40</v>
+        <v>52.94964028776978</v>
       </c>
     </row>
     <row r="45">
@@ -1988,171 +1988,171 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>PAUCAR DEL SARA SARA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>727</v>
+        <v>355</v>
       </c>
       <c r="E45" t="n">
-        <v>341</v>
+        <v>241</v>
       </c>
       <c r="F45" t="n">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="G45" t="n">
-        <v>248</v>
+        <v>47</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>46.9050894085282</v>
+        <v>67.88732394366197</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>VICTOR FAJARDO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1667</v>
+        <v>727</v>
       </c>
       <c r="E46" t="n">
-        <v>569</v>
+        <v>503</v>
       </c>
       <c r="F46" t="n">
-        <v>346</v>
+        <v>157</v>
       </c>
       <c r="G46" t="n">
-        <v>90</v>
+        <v>296</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="I46" t="n">
-        <v>34.13317336532693</v>
+        <v>69.18844566712518</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANDIA</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1350</v>
+        <v>1667</v>
       </c>
       <c r="E47" t="n">
-        <v>344</v>
+        <v>1134</v>
       </c>
       <c r="F47" t="n">
-        <v>172</v>
+        <v>766</v>
       </c>
       <c r="G47" t="n">
-        <v>125</v>
+        <v>188</v>
       </c>
       <c r="H47" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>25.48148148148148</v>
+        <v>68.02639472105579</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SANDIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1082</v>
+        <v>1350</v>
       </c>
       <c r="E48" t="n">
-        <v>73</v>
+        <v>619</v>
       </c>
       <c r="F48" t="n">
-        <v>64</v>
+        <v>394</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>170</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I48" t="n">
-        <v>6.746765249537892</v>
+        <v>45.85185185185185</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>320</v>
+        <v>1082</v>
       </c>
       <c r="E49" t="n">
-        <v>237</v>
+        <v>319</v>
       </c>
       <c r="F49" t="n">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="G49" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I49" t="n">
-        <v>74.0625</v>
+        <v>29.48243992606285</v>
       </c>
     </row>
     <row r="50">
@@ -2168,61 +2168,96 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="E50" t="n">
-        <v>46</v>
+        <v>278</v>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="G50" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>16.97416974169742</v>
+        <v>86.875</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CHACHAPOYAS</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="E51" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F51" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>39.44954128440367</v>
+        <v>16.97416974169742</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SONCHE</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>109</v>
+      </c>
+      <c r="E52" t="n">
+        <v>66</v>
+      </c>
+      <c r="F52" t="n">
+        <v>27</v>
+      </c>
+      <c r="G52" t="n">
+        <v>39</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>60.55045871559633</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -495,19 +495,19 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>6761</v>
+        <v>10321</v>
       </c>
       <c r="F2" t="n">
-        <v>1818</v>
+        <v>3035</v>
       </c>
       <c r="G2" t="n">
-        <v>4691</v>
+        <v>6877</v>
       </c>
       <c r="H2" t="n">
-        <v>245</v>
+        <v>407</v>
       </c>
       <c r="I2" t="n">
-        <v>54.90498619457528</v>
+        <v>83.81516972551567</v>
       </c>
     </row>
     <row r="3">
@@ -565,19 +565,19 @@
         <v>160</v>
       </c>
       <c r="E4" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H4" t="n">
         <v>48</v>
       </c>
       <c r="I4" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -600,19 +600,19 @@
         <v>1016</v>
       </c>
       <c r="E5" t="n">
-        <v>600</v>
+        <v>745</v>
       </c>
       <c r="F5" t="n">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="G5" t="n">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>59.05511811023622</v>
+        <v>73.3267716535433</v>
       </c>
     </row>
     <row r="6">
@@ -635,19 +635,19 @@
         <v>5767</v>
       </c>
       <c r="E6" t="n">
-        <v>4193</v>
+        <v>5609</v>
       </c>
       <c r="F6" t="n">
-        <v>1230</v>
+        <v>1609</v>
       </c>
       <c r="G6" t="n">
-        <v>2885</v>
+        <v>3923</v>
       </c>
       <c r="H6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I6" t="n">
-        <v>72.7067799549159</v>
+        <v>97.26027397260275</v>
       </c>
     </row>
     <row r="7">
@@ -670,19 +670,19 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>613</v>
+        <v>1609</v>
       </c>
       <c r="F7" t="n">
-        <v>235</v>
+        <v>575</v>
       </c>
       <c r="G7" t="n">
-        <v>367</v>
+        <v>1019</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>24.67793880837359</v>
+        <v>64.77455716586151</v>
       </c>
     </row>
     <row r="8">
@@ -705,19 +705,19 @@
         <v>473</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>343</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>234</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>24.52431289640592</v>
+        <v>72.51585623678648</v>
       </c>
     </row>
     <row r="9">
@@ -740,19 +740,19 @@
         <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>74.61538461538461</v>
+        <v>87.69230769230769</v>
       </c>
     </row>
     <row r="10">
@@ -775,19 +775,19 @@
         <v>401</v>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>341</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="G10" t="n">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>29.42643391521197</v>
+        <v>85.03740648379052</v>
       </c>
     </row>
     <row r="11">
@@ -810,19 +810,19 @@
         <v>175</v>
       </c>
       <c r="E11" t="n">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F11" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>66.28571428571428</v>
+        <v>89.71428571428571</v>
       </c>
     </row>
     <row r="12">
@@ -845,19 +845,19 @@
         <v>473</v>
       </c>
       <c r="E12" t="n">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="F12" t="n">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="G12" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>79.70401691331924</v>
+        <v>89.21775898520085</v>
       </c>
     </row>
     <row r="13">
@@ -880,19 +880,19 @@
         <v>392</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>304</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>22.19387755102041</v>
+        <v>77.55102040816327</v>
       </c>
     </row>
     <row r="14">
@@ -915,19 +915,19 @@
         <v>627</v>
       </c>
       <c r="E14" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>57.57575757575758</v>
+        <v>71.45135566188198</v>
       </c>
     </row>
     <row r="15">
@@ -950,19 +950,19 @@
         <v>1492</v>
       </c>
       <c r="E15" t="n">
-        <v>805</v>
+        <v>1110</v>
       </c>
       <c r="F15" t="n">
-        <v>535</v>
+        <v>766</v>
       </c>
       <c r="G15" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="H15" t="n">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="I15" t="n">
-        <v>53.95442359249329</v>
+        <v>74.39678284182307</v>
       </c>
     </row>
     <row r="16">
@@ -985,19 +985,19 @@
         <v>7067</v>
       </c>
       <c r="E16" t="n">
-        <v>3099</v>
+        <v>3803</v>
       </c>
       <c r="F16" t="n">
-        <v>1571</v>
+        <v>1868</v>
       </c>
       <c r="G16" t="n">
-        <v>785</v>
+        <v>944</v>
       </c>
       <c r="H16" t="n">
-        <v>748</v>
+        <v>1000</v>
       </c>
       <c r="I16" t="n">
-        <v>43.85170510824961</v>
+        <v>53.81349936323758</v>
       </c>
     </row>
     <row r="17">
@@ -1020,19 +1020,19 @@
         <v>1401</v>
       </c>
       <c r="E17" t="n">
-        <v>617</v>
+        <v>1322</v>
       </c>
       <c r="F17" t="n">
-        <v>481</v>
+        <v>1056</v>
       </c>
       <c r="G17" t="n">
-        <v>136</v>
+        <v>266</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>44.03997144896503</v>
+        <v>94.36117059243398</v>
       </c>
     </row>
     <row r="18">
@@ -1055,19 +1055,19 @@
         <v>544</v>
       </c>
       <c r="E18" t="n">
-        <v>350</v>
+        <v>505</v>
       </c>
       <c r="F18" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="G18" t="n">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="I18" t="n">
-        <v>64.33823529411765</v>
+        <v>92.83088235294117</v>
       </c>
     </row>
     <row r="19">
@@ -1090,19 +1090,19 @@
         <v>524</v>
       </c>
       <c r="E19" t="n">
-        <v>222</v>
+        <v>510</v>
       </c>
       <c r="F19" t="n">
-        <v>98</v>
+        <v>278</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>220</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>42.36641221374045</v>
+        <v>97.32824427480917</v>
       </c>
     </row>
     <row r="20">
@@ -1125,19 +1125,19 @@
         <v>161</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>31.67701863354037</v>
+        <v>72.67080745341616</v>
       </c>
     </row>
     <row r="21">
@@ -1160,19 +1160,19 @@
         <v>807</v>
       </c>
       <c r="E21" t="n">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="F21" t="n">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="G21" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H21" t="n">
         <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>21.8091697645601</v>
+        <v>30.11152416356878</v>
       </c>
     </row>
     <row r="22">
@@ -1195,19 +1195,19 @@
         <v>515</v>
       </c>
       <c r="E22" t="n">
-        <v>243</v>
+        <v>366</v>
       </c>
       <c r="F22" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="G22" t="n">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="H22" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I22" t="n">
-        <v>47.18446601941748</v>
+        <v>71.06796116504854</v>
       </c>
     </row>
     <row r="23">
@@ -1230,19 +1230,19 @@
         <v>1051</v>
       </c>
       <c r="E23" t="n">
-        <v>528</v>
+        <v>766</v>
       </c>
       <c r="F23" t="n">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="G23" t="n">
-        <v>302</v>
+        <v>451</v>
       </c>
       <c r="H23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>50.23786869647955</v>
+        <v>72.88296860133207</v>
       </c>
     </row>
     <row r="24">
@@ -1265,19 +1265,19 @@
         <v>2404</v>
       </c>
       <c r="E24" t="n">
-        <v>1777</v>
+        <v>2228</v>
       </c>
       <c r="F24" t="n">
-        <v>1325</v>
+        <v>1601</v>
       </c>
       <c r="G24" t="n">
-        <v>418</v>
+        <v>540</v>
       </c>
       <c r="H24" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="I24" t="n">
-        <v>73.91846921797006</v>
+        <v>92.67886855241264</v>
       </c>
     </row>
     <row r="25">
@@ -1300,19 +1300,19 @@
         <v>761</v>
       </c>
       <c r="E25" t="n">
-        <v>453</v>
+        <v>627</v>
       </c>
       <c r="F25" t="n">
-        <v>393</v>
+        <v>539</v>
       </c>
       <c r="G25" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>59.526938239159</v>
+        <v>82.3915900131406</v>
       </c>
     </row>
     <row r="26">
@@ -1335,19 +1335,19 @@
         <v>841</v>
       </c>
       <c r="E26" t="n">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="G26" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>14.62544589774079</v>
+        <v>24.73246135552913</v>
       </c>
     </row>
     <row r="27">
@@ -1370,19 +1370,19 @@
         <v>1019</v>
       </c>
       <c r="E27" t="n">
-        <v>377</v>
+        <v>444</v>
       </c>
       <c r="F27" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G27" t="n">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="H27" t="n">
         <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.99705593719333</v>
+        <v>43.57212953876349</v>
       </c>
     </row>
     <row r="28">
@@ -1405,19 +1405,19 @@
         <v>1251</v>
       </c>
       <c r="E28" t="n">
-        <v>576</v>
+        <v>949</v>
       </c>
       <c r="F28" t="n">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="G28" t="n">
-        <v>439</v>
+        <v>726</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>46.0431654676259</v>
+        <v>75.85931254996004</v>
       </c>
     </row>
     <row r="29">
@@ -1440,19 +1440,19 @@
         <v>728</v>
       </c>
       <c r="E29" t="n">
-        <v>491</v>
+        <v>679</v>
       </c>
       <c r="F29" t="n">
-        <v>271</v>
+        <v>396</v>
       </c>
       <c r="G29" t="n">
-        <v>215</v>
+        <v>278</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>67.44505494505495</v>
+        <v>93.26923076923077</v>
       </c>
     </row>
     <row r="30">
@@ -1475,19 +1475,19 @@
         <v>525</v>
       </c>
       <c r="E30" t="n">
-        <v>445</v>
+        <v>512</v>
       </c>
       <c r="F30" t="n">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="G30" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>84.76190476190476</v>
+        <v>97.52380952380952</v>
       </c>
     </row>
     <row r="31">
@@ -1510,19 +1510,19 @@
         <v>236</v>
       </c>
       <c r="E31" t="n">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c r="F31" t="n">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>61.86440677966102</v>
+        <v>97.45762711864407</v>
       </c>
     </row>
     <row r="32">
@@ -1545,19 +1545,19 @@
         <v>734</v>
       </c>
       <c r="E32" t="n">
-        <v>447</v>
+        <v>539</v>
       </c>
       <c r="F32" t="n">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="G32" t="n">
-        <v>298</v>
+        <v>366</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>60.89918256130791</v>
+        <v>73.43324250681199</v>
       </c>
     </row>
     <row r="33">
@@ -1615,19 +1615,19 @@
         <v>246</v>
       </c>
       <c r="E34" t="n">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="F34" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G34" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>54.87804878048781</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="35">
@@ -1685,19 +1685,19 @@
         <v>180</v>
       </c>
       <c r="E36" t="n">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="F36" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G36" t="n">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
@@ -1720,19 +1720,19 @@
         <v>1902</v>
       </c>
       <c r="E37" t="n">
-        <v>1002</v>
+        <v>1654</v>
       </c>
       <c r="F37" t="n">
-        <v>257</v>
+        <v>464</v>
       </c>
       <c r="G37" t="n">
-        <v>731</v>
+        <v>1178</v>
       </c>
       <c r="H37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" t="n">
-        <v>52.6813880126183</v>
+        <v>86.96109358569927</v>
       </c>
     </row>
     <row r="38">
@@ -1755,19 +1755,19 @@
         <v>241</v>
       </c>
       <c r="E38" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>64.31535269709543</v>
+        <v>73.02904564315352</v>
       </c>
     </row>
     <row r="39">
@@ -1790,19 +1790,19 @@
         <v>1075</v>
       </c>
       <c r="E39" t="n">
-        <v>430</v>
+        <v>543</v>
       </c>
       <c r="F39" t="n">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="G39" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I39" t="n">
-        <v>40</v>
+        <v>50.51162790697674</v>
       </c>
     </row>
     <row r="40">
@@ -1825,19 +1825,19 @@
         <v>990</v>
       </c>
       <c r="E40" t="n">
-        <v>746</v>
+        <v>870</v>
       </c>
       <c r="F40" t="n">
-        <v>460</v>
+        <v>549</v>
       </c>
       <c r="G40" t="n">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="H40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I40" t="n">
-        <v>75.35353535353535</v>
+        <v>87.87878787878788</v>
       </c>
     </row>
     <row r="41">
@@ -1860,19 +1860,19 @@
         <v>2150</v>
       </c>
       <c r="E41" t="n">
-        <v>693</v>
+        <v>1009</v>
       </c>
       <c r="F41" t="n">
-        <v>238</v>
+        <v>369</v>
       </c>
       <c r="G41" t="n">
-        <v>434</v>
+        <v>611</v>
       </c>
       <c r="H41" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I41" t="n">
-        <v>32.23255813953488</v>
+        <v>46.93023255813954</v>
       </c>
     </row>
     <row r="42">
@@ -1895,19 +1895,19 @@
         <v>1644</v>
       </c>
       <c r="E42" t="n">
-        <v>930</v>
+        <v>1195</v>
       </c>
       <c r="F42" t="n">
-        <v>582</v>
+        <v>771</v>
       </c>
       <c r="G42" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="H42" t="n">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="I42" t="n">
-        <v>56.56934306569343</v>
+        <v>72.68856447688565</v>
       </c>
     </row>
     <row r="43">
@@ -1930,19 +1930,19 @@
         <v>728</v>
       </c>
       <c r="E43" t="n">
-        <v>486</v>
+        <v>707</v>
       </c>
       <c r="F43" t="n">
-        <v>392</v>
+        <v>540</v>
       </c>
       <c r="G43" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="I43" t="n">
-        <v>66.75824175824175</v>
+        <v>97.11538461538461</v>
       </c>
     </row>
     <row r="44">
@@ -1965,19 +1965,19 @@
         <v>695</v>
       </c>
       <c r="E44" t="n">
-        <v>368</v>
+        <v>478</v>
       </c>
       <c r="F44" t="n">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="G44" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="H44" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="I44" t="n">
-        <v>52.94964028776978</v>
+        <v>68.77697841726619</v>
       </c>
     </row>
     <row r="45">
@@ -2000,10 +2000,10 @@
         <v>355</v>
       </c>
       <c r="E45" t="n">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="F45" t="n">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="G45" t="n">
         <v>47</v>
@@ -2012,7 +2012,7 @@
         <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>67.88732394366197</v>
+        <v>75.49295774647888</v>
       </c>
     </row>
     <row r="46">
@@ -2035,19 +2035,19 @@
         <v>727</v>
       </c>
       <c r="E46" t="n">
-        <v>503</v>
+        <v>692</v>
       </c>
       <c r="F46" t="n">
-        <v>157</v>
+        <v>236</v>
       </c>
       <c r="G46" t="n">
-        <v>296</v>
+        <v>381</v>
       </c>
       <c r="H46" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="I46" t="n">
-        <v>69.18844566712518</v>
+        <v>95.1856946354883</v>
       </c>
     </row>
     <row r="47">
@@ -2070,19 +2070,19 @@
         <v>1667</v>
       </c>
       <c r="E47" t="n">
-        <v>1134</v>
+        <v>1598</v>
       </c>
       <c r="F47" t="n">
-        <v>766</v>
+        <v>1094</v>
       </c>
       <c r="G47" t="n">
-        <v>188</v>
+        <v>292</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I47" t="n">
-        <v>68.02639472105579</v>
+        <v>95.86082783443311</v>
       </c>
     </row>
     <row r="48">
@@ -2105,19 +2105,19 @@
         <v>1350</v>
       </c>
       <c r="E48" t="n">
-        <v>619</v>
+        <v>998</v>
       </c>
       <c r="F48" t="n">
-        <v>394</v>
+        <v>716</v>
       </c>
       <c r="G48" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="H48" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="I48" t="n">
-        <v>45.85185185185185</v>
+        <v>73.92592592592592</v>
       </c>
     </row>
     <row r="49">
@@ -2140,19 +2140,19 @@
         <v>1082</v>
       </c>
       <c r="E49" t="n">
-        <v>319</v>
+        <v>487</v>
       </c>
       <c r="F49" t="n">
-        <v>218</v>
+        <v>327</v>
       </c>
       <c r="G49" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I49" t="n">
-        <v>29.48243992606285</v>
+        <v>45.00924214417745</v>
       </c>
     </row>
     <row r="50">
@@ -2175,19 +2175,19 @@
         <v>320</v>
       </c>
       <c r="E50" t="n">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="F50" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="G50" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>86.875</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="51">
@@ -2210,19 +2210,19 @@
         <v>271</v>
       </c>
       <c r="E51" t="n">
-        <v>46</v>
+        <v>270</v>
       </c>
       <c r="F51" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="G51" t="n">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>16.97416974169742</v>
+        <v>99.63099630996311</v>
       </c>
     </row>
     <row r="52">
@@ -2245,19 +2245,19 @@
         <v>109</v>
       </c>
       <c r="E52" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="F52" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G52" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>60.55045871559633</v>
+        <v>81.65137614678899</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -495,19 +495,19 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>10321</v>
+        <v>10325</v>
       </c>
       <c r="F2" t="n">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="G2" t="n">
-        <v>6877</v>
+        <v>6879</v>
       </c>
       <c r="H2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I2" t="n">
-        <v>83.81516972551567</v>
+        <v>83.84765307779762</v>
       </c>
     </row>
     <row r="3">
@@ -670,10 +670,10 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="F7" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G7" t="n">
         <v>1019</v>
@@ -682,7 +682,7 @@
         <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>64.77455716586151</v>
+        <v>64.81481481481481</v>
       </c>
     </row>
     <row r="8">
@@ -2070,10 +2070,10 @@
         <v>1667</v>
       </c>
       <c r="E47" t="n">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="F47" t="n">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G47" t="n">
         <v>292</v>
@@ -2082,7 +2082,7 @@
         <v>22</v>
       </c>
       <c r="I47" t="n">
-        <v>95.86082783443311</v>
+        <v>95.92081583683263</v>
       </c>
     </row>
     <row r="48">

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,19 +495,19 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>10325</v>
+        <v>11422</v>
       </c>
       <c r="F2" t="n">
-        <v>3036</v>
+        <v>3407</v>
       </c>
       <c r="G2" t="n">
-        <v>6879</v>
+        <v>7562</v>
       </c>
       <c r="H2" t="n">
-        <v>408</v>
+        <v>455</v>
       </c>
       <c r="I2" t="n">
-        <v>83.84765307779762</v>
+        <v>92.75621244112392</v>
       </c>
     </row>
     <row r="3">
@@ -600,19 +600,19 @@
         <v>1016</v>
       </c>
       <c r="E5" t="n">
-        <v>745</v>
+        <v>1013</v>
       </c>
       <c r="F5" t="n">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="G5" t="n">
-        <v>423</v>
+        <v>637</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>73.3267716535433</v>
+        <v>99.70472440944881</v>
       </c>
     </row>
     <row r="6">
@@ -635,19 +635,19 @@
         <v>5767</v>
       </c>
       <c r="E6" t="n">
-        <v>5609</v>
+        <v>5643</v>
       </c>
       <c r="F6" t="n">
-        <v>1609</v>
+        <v>1618</v>
       </c>
       <c r="G6" t="n">
-        <v>3923</v>
+        <v>3950</v>
       </c>
       <c r="H6" t="n">
         <v>71</v>
       </c>
       <c r="I6" t="n">
-        <v>97.26027397260275</v>
+        <v>97.84983526963759</v>
       </c>
     </row>
     <row r="7">
@@ -670,19 +670,19 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>1610</v>
+        <v>2016</v>
       </c>
       <c r="F7" t="n">
-        <v>576</v>
+        <v>776</v>
       </c>
       <c r="G7" t="n">
-        <v>1019</v>
+        <v>1242</v>
       </c>
       <c r="H7" t="n">
         <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>64.81481481481481</v>
+        <v>81.15942028985508</v>
       </c>
     </row>
     <row r="8">
@@ -705,19 +705,19 @@
         <v>473</v>
       </c>
       <c r="E8" t="n">
-        <v>343</v>
+        <v>464</v>
       </c>
       <c r="F8" t="n">
-        <v>234</v>
+        <v>333</v>
       </c>
       <c r="G8" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>72.51585623678648</v>
+        <v>98.09725158562368</v>
       </c>
     </row>
     <row r="9">
@@ -728,66 +728,66 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RECUAY</t>
+          <t>OCROS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>SAN CRISTOBAL DE RAJAN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>87.69230769230769</v>
+        <v>0.4784688995215311</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>RECUAY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>401</v>
+        <v>130</v>
       </c>
       <c r="E10" t="n">
-        <v>341</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="G10" t="n">
-        <v>184</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>85.03740648379052</v>
+        <v>99.23076923076923</v>
       </c>
     </row>
     <row r="11">
@@ -798,31 +798,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>175</v>
+        <v>401</v>
       </c>
       <c r="E11" t="n">
-        <v>157</v>
+        <v>397</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="G11" t="n">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>89.71428571428571</v>
+        <v>99.00249376558602</v>
       </c>
     </row>
     <row r="12">
@@ -838,61 +838,61 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>473</v>
+        <v>175</v>
       </c>
       <c r="E12" t="n">
-        <v>422</v>
+        <v>175</v>
       </c>
       <c r="F12" t="n">
-        <v>263</v>
+        <v>109</v>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>89.21775898520085</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REQUENA</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>392</v>
+        <v>473</v>
       </c>
       <c r="E13" t="n">
-        <v>304</v>
+        <v>469</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>302</v>
       </c>
       <c r="G13" t="n">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>77.55102040816327</v>
+        <v>99.15433403805497</v>
       </c>
     </row>
     <row r="14">
@@ -908,61 +908,61 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>627</v>
+        <v>392</v>
       </c>
       <c r="E14" t="n">
-        <v>448</v>
+        <v>304</v>
       </c>
       <c r="F14" t="n">
         <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>375</v>
+        <v>233</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>71.45135566188198</v>
+        <v>77.55102040816327</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>REQUENA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1492</v>
+        <v>627</v>
       </c>
       <c r="E15" t="n">
-        <v>1110</v>
+        <v>543</v>
       </c>
       <c r="F15" t="n">
-        <v>766</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>226</v>
+        <v>466</v>
       </c>
       <c r="H15" t="n">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>74.39678284182307</v>
+        <v>86.60287081339713</v>
       </c>
     </row>
     <row r="16">
@@ -973,66 +973,66 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7067</v>
+        <v>1492</v>
       </c>
       <c r="E16" t="n">
-        <v>3803</v>
+        <v>1421</v>
       </c>
       <c r="F16" t="n">
-        <v>1868</v>
+        <v>964</v>
       </c>
       <c r="G16" t="n">
-        <v>944</v>
+        <v>258</v>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>199</v>
       </c>
       <c r="I16" t="n">
-        <v>53.81349936323758</v>
+        <v>95.24128686327077</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1401</v>
+        <v>7067</v>
       </c>
       <c r="E17" t="n">
-        <v>1322</v>
+        <v>5801</v>
       </c>
       <c r="F17" t="n">
-        <v>1056</v>
+        <v>2738</v>
       </c>
       <c r="G17" t="n">
-        <v>266</v>
+        <v>1363</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1714</v>
       </c>
       <c r="I17" t="n">
-        <v>94.36117059243398</v>
+        <v>82.0857506721381</v>
       </c>
     </row>
     <row r="18">
@@ -1043,66 +1043,66 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YAULI</t>
+          <t>SATIPO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>544</v>
+        <v>1401</v>
       </c>
       <c r="E18" t="n">
-        <v>505</v>
+        <v>1343</v>
       </c>
       <c r="F18" t="n">
-        <v>168</v>
+        <v>1070</v>
       </c>
       <c r="G18" t="n">
-        <v>199</v>
+        <v>271</v>
       </c>
       <c r="H18" t="n">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>92.83088235294117</v>
+        <v>95.86009992862242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>YAULI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F19" t="n">
-        <v>278</v>
+        <v>168</v>
       </c>
       <c r="G19" t="n">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="I19" t="n">
-        <v>97.32824427480917</v>
+        <v>92.83088235294117</v>
       </c>
     </row>
     <row r="20">
@@ -1118,131 +1118,131 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>161</v>
+        <v>524</v>
       </c>
       <c r="E20" t="n">
-        <v>117</v>
+        <v>510</v>
       </c>
       <c r="F20" t="n">
-        <v>66</v>
+        <v>278</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="H20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>72.67080745341616</v>
+        <v>97.32824427480917</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>807</v>
+        <v>161</v>
       </c>
       <c r="E21" t="n">
-        <v>243</v>
+        <v>161</v>
       </c>
       <c r="F21" t="n">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="I21" t="n">
-        <v>30.11152416356878</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TARATA</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>515</v>
+        <v>807</v>
       </c>
       <c r="E22" t="n">
-        <v>366</v>
+        <v>265</v>
       </c>
       <c r="F22" t="n">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="G22" t="n">
-        <v>235</v>
+        <v>49</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>71.06796116504854</v>
+        <v>32.83767038413878</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TARATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1051</v>
+        <v>515</v>
       </c>
       <c r="E23" t="n">
-        <v>766</v>
+        <v>512</v>
       </c>
       <c r="F23" t="n">
-        <v>291</v>
+        <v>147</v>
       </c>
       <c r="G23" t="n">
-        <v>451</v>
+        <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="I23" t="n">
-        <v>72.88296860133207</v>
+        <v>99.41747572815534</v>
       </c>
     </row>
     <row r="24">
@@ -1253,31 +1253,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LEONCIO PRADO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2404</v>
+        <v>1051</v>
       </c>
       <c r="E24" t="n">
-        <v>2228</v>
+        <v>976</v>
       </c>
       <c r="F24" t="n">
-        <v>1601</v>
+        <v>379</v>
       </c>
       <c r="G24" t="n">
-        <v>540</v>
+        <v>573</v>
       </c>
       <c r="H24" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="I24" t="n">
-        <v>92.67886855241264</v>
+        <v>92.8639391056137</v>
       </c>
     </row>
     <row r="25">
@@ -1288,31 +1288,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MARAÑON</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>761</v>
+        <v>2404</v>
       </c>
       <c r="E25" t="n">
-        <v>627</v>
+        <v>2314</v>
       </c>
       <c r="F25" t="n">
-        <v>539</v>
+        <v>1665</v>
       </c>
       <c r="G25" t="n">
-        <v>75</v>
+        <v>561</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="I25" t="n">
-        <v>82.3915900131406</v>
+        <v>96.25623960066557</v>
       </c>
     </row>
     <row r="26">
@@ -1328,26 +1328,26 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>841</v>
+        <v>761</v>
       </c>
       <c r="E26" t="n">
-        <v>208</v>
+        <v>746</v>
       </c>
       <c r="F26" t="n">
-        <v>141</v>
+        <v>650</v>
       </c>
       <c r="G26" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I26" t="n">
-        <v>24.73246135552913</v>
+        <v>98.02890932982918</v>
       </c>
     </row>
     <row r="27">
@@ -1358,31 +1358,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YAROWILCA</t>
+          <t>MARAÑON</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1019</v>
+        <v>841</v>
       </c>
       <c r="E27" t="n">
-        <v>444</v>
+        <v>276</v>
       </c>
       <c r="F27" t="n">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="G27" t="n">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>43.57212953876349</v>
+        <v>32.81807372175981</v>
       </c>
     </row>
     <row r="28">
@@ -1398,26 +1398,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1251</v>
+        <v>1019</v>
       </c>
       <c r="E28" t="n">
-        <v>949</v>
+        <v>549</v>
       </c>
       <c r="F28" t="n">
-        <v>223</v>
+        <v>98</v>
       </c>
       <c r="G28" t="n">
-        <v>726</v>
+        <v>445</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>75.85931254996004</v>
+        <v>53.87634936211973</v>
       </c>
     </row>
     <row r="29">
@@ -1433,61 +1433,61 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>728</v>
+        <v>1251</v>
       </c>
       <c r="E29" t="n">
-        <v>679</v>
+        <v>1149</v>
       </c>
       <c r="F29" t="n">
-        <v>396</v>
+        <v>264</v>
       </c>
       <c r="G29" t="n">
-        <v>278</v>
+        <v>885</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>93.26923076923077</v>
+        <v>91.84652278177458</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>YAROWILCA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>525</v>
+        <v>728</v>
       </c>
       <c r="E30" t="n">
-        <v>512</v>
+        <v>725</v>
       </c>
       <c r="F30" t="n">
-        <v>295</v>
+        <v>427</v>
       </c>
       <c r="G30" t="n">
-        <v>204</v>
+        <v>291</v>
       </c>
       <c r="H30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I30" t="n">
-        <v>97.52380952380952</v>
+        <v>99.58791208791209</v>
       </c>
     </row>
     <row r="31">
@@ -1503,96 +1503,96 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>236</v>
+        <v>525</v>
       </c>
       <c r="E31" t="n">
-        <v>230</v>
+        <v>512</v>
       </c>
       <c r="F31" t="n">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="G31" t="n">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>97.45762711864407</v>
+        <v>97.52380952380952</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TOCACHE</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>734</v>
+        <v>236</v>
       </c>
       <c r="E32" t="n">
-        <v>539</v>
+        <v>234</v>
       </c>
       <c r="F32" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="G32" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>73.43324250681199</v>
+        <v>99.15254237288136</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TOCACHE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>230</v>
+        <v>734</v>
       </c>
       <c r="E33" t="n">
-        <v>172</v>
+        <v>734</v>
       </c>
       <c r="F33" t="n">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="G33" t="n">
-        <v>72</v>
+        <v>524</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>74.78260869565217</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -1608,26 +1608,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="E34" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F34" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="G34" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>66.66666666666666</v>
+        <v>74.78260869565217</v>
       </c>
     </row>
     <row r="35">
@@ -1643,26 +1643,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="E35" t="n">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="G35" t="n">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>93.4959349593496</v>
       </c>
     </row>
     <row r="36">
@@ -1678,20 +1678,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="E36" t="n">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="F36" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G36" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1703,106 +1703,106 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1902</v>
+        <v>180</v>
       </c>
       <c r="E37" t="n">
-        <v>1654</v>
+        <v>180</v>
       </c>
       <c r="F37" t="n">
-        <v>464</v>
+        <v>74</v>
       </c>
       <c r="G37" t="n">
-        <v>1178</v>
+        <v>106</v>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>86.96109358569927</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>241</v>
+        <v>1902</v>
       </c>
       <c r="E38" t="n">
-        <v>176</v>
+        <v>1861</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>547</v>
       </c>
       <c r="G38" t="n">
-        <v>168</v>
+        <v>1302</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I38" t="n">
-        <v>73.02904564315352</v>
+        <v>97.84437434279705</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1075</v>
+        <v>241</v>
       </c>
       <c r="E39" t="n">
-        <v>543</v>
+        <v>240</v>
       </c>
       <c r="F39" t="n">
-        <v>334</v>
+        <v>14</v>
       </c>
       <c r="G39" t="n">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="H39" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>50.51162790697674</v>
+        <v>99.5850622406639</v>
       </c>
     </row>
     <row r="40">
@@ -1818,26 +1818,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>990</v>
+        <v>1075</v>
       </c>
       <c r="E40" t="n">
-        <v>870</v>
+        <v>830</v>
       </c>
       <c r="F40" t="n">
-        <v>549</v>
+        <v>482</v>
       </c>
       <c r="G40" t="n">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="H40" t="n">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I40" t="n">
-        <v>87.87878787878788</v>
+        <v>77.20930232558139</v>
       </c>
     </row>
     <row r="41">
@@ -1853,26 +1853,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2150</v>
+        <v>990</v>
       </c>
       <c r="E41" t="n">
-        <v>1009</v>
+        <v>977</v>
       </c>
       <c r="F41" t="n">
-        <v>369</v>
+        <v>599</v>
       </c>
       <c r="G41" t="n">
-        <v>611</v>
+        <v>307</v>
       </c>
       <c r="H41" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I41" t="n">
-        <v>46.93023255813954</v>
+        <v>98.68686868686869</v>
       </c>
     </row>
     <row r="42">
@@ -1883,31 +1883,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAMANA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1644</v>
+        <v>2150</v>
       </c>
       <c r="E42" t="n">
-        <v>1195</v>
+        <v>1854</v>
       </c>
       <c r="F42" t="n">
-        <v>771</v>
+        <v>621</v>
       </c>
       <c r="G42" t="n">
-        <v>158</v>
+        <v>1108</v>
       </c>
       <c r="H42" t="n">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="I42" t="n">
-        <v>72.68856447688565</v>
+        <v>86.23255813953489</v>
       </c>
     </row>
     <row r="43">
@@ -1918,66 +1918,66 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CARAVELI</t>
+          <t>CAMANA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>728</v>
+        <v>1644</v>
       </c>
       <c r="E43" t="n">
-        <v>707</v>
+        <v>1587</v>
       </c>
       <c r="F43" t="n">
-        <v>540</v>
+        <v>1009</v>
       </c>
       <c r="G43" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="H43" t="n">
-        <v>71</v>
+        <v>379</v>
       </c>
       <c r="I43" t="n">
-        <v>97.11538461538461</v>
+        <v>96.53284671532847</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LUCANAS</t>
+          <t>CARAVELI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>695</v>
+        <v>728</v>
       </c>
       <c r="E44" t="n">
-        <v>478</v>
+        <v>726</v>
       </c>
       <c r="F44" t="n">
-        <v>281</v>
+        <v>556</v>
       </c>
       <c r="G44" t="n">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="H44" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="I44" t="n">
-        <v>68.77697841726619</v>
+        <v>99.72527472527473</v>
       </c>
     </row>
     <row r="45">
@@ -1988,31 +1988,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PAUCAR DEL SARA SARA</t>
+          <t>LUCANAS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D45" t="n">
+        <v>695</v>
+      </c>
+      <c r="E45" t="n">
+        <v>595</v>
+      </c>
+      <c r="F45" t="n">
         <v>355</v>
       </c>
-      <c r="E45" t="n">
-        <v>268</v>
-      </c>
-      <c r="F45" t="n">
-        <v>218</v>
-      </c>
       <c r="G45" t="n">
-        <v>47</v>
+        <v>185</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="I45" t="n">
-        <v>75.49295774647888</v>
+        <v>85.61151079136691</v>
       </c>
     </row>
     <row r="46">
@@ -2023,171 +2023,171 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>PAUCAR DEL SARA SARA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>727</v>
+        <v>355</v>
       </c>
       <c r="E46" t="n">
-        <v>692</v>
+        <v>298</v>
       </c>
       <c r="F46" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="G46" t="n">
-        <v>381</v>
+        <v>52</v>
       </c>
       <c r="H46" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>95.1856946354883</v>
+        <v>83.94366197183099</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>VICTOR FAJARDO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1667</v>
+        <v>727</v>
       </c>
       <c r="E47" t="n">
-        <v>1599</v>
+        <v>726</v>
       </c>
       <c r="F47" t="n">
-        <v>1095</v>
+        <v>257</v>
       </c>
       <c r="G47" t="n">
-        <v>292</v>
+        <v>394</v>
       </c>
       <c r="H47" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="I47" t="n">
-        <v>95.92081583683263</v>
+        <v>99.86244841815682</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANDIA</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1350</v>
+        <v>1667</v>
       </c>
       <c r="E48" t="n">
-        <v>998</v>
+        <v>1638</v>
       </c>
       <c r="F48" t="n">
-        <v>716</v>
+        <v>1133</v>
       </c>
       <c r="G48" t="n">
-        <v>210</v>
+        <v>314</v>
       </c>
       <c r="H48" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="I48" t="n">
-        <v>73.92592592592592</v>
+        <v>98.26034793041391</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SANDIA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1082</v>
+        <v>1350</v>
       </c>
       <c r="E49" t="n">
-        <v>487</v>
+        <v>1274</v>
       </c>
       <c r="F49" t="n">
-        <v>327</v>
+        <v>870</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="H49" t="n">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="I49" t="n">
-        <v>45.00924214417745</v>
+        <v>94.37037037037037</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>320</v>
+        <v>1082</v>
       </c>
       <c r="E50" t="n">
-        <v>296</v>
+        <v>833</v>
       </c>
       <c r="F50" t="n">
-        <v>178</v>
+        <v>487</v>
       </c>
       <c r="G50" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="I50" t="n">
-        <v>92.5</v>
+        <v>76.98706099815156</v>
       </c>
     </row>
     <row r="51">
@@ -2203,61 +2203,96 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="E51" t="n">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="F51" t="n">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="G51" t="n">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>99.63099630996311</v>
+        <v>95.3125</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHACHAPOYAS</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="E52" t="n">
-        <v>89</v>
+        <v>270</v>
       </c>
       <c r="F52" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="G52" t="n">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>81.65137614678899</v>
+        <v>99.63099630996311</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SONCHE</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>109</v>
+      </c>
+      <c r="E53" t="n">
+        <v>109</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29</v>
+      </c>
+      <c r="G53" t="n">
+        <v>80</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,19 +495,19 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>11422</v>
+        <v>4525</v>
       </c>
       <c r="F2" t="n">
-        <v>3407</v>
+        <v>1067</v>
       </c>
       <c r="G2" t="n">
-        <v>7562</v>
+        <v>3236</v>
       </c>
       <c r="H2" t="n">
-        <v>455</v>
+        <v>215</v>
       </c>
       <c r="I2" t="n">
-        <v>92.75621244112392</v>
+        <v>36.74679226896216</v>
       </c>
     </row>
     <row r="3">
@@ -530,19 +530,19 @@
         <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>45.76271186440678</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>160</v>
       </c>
       <c r="E4" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
         <v>48</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="5">
@@ -600,19 +600,19 @@
         <v>1016</v>
       </c>
       <c r="E5" t="n">
-        <v>1013</v>
+        <v>437</v>
       </c>
       <c r="F5" t="n">
-        <v>377</v>
+        <v>148</v>
       </c>
       <c r="G5" t="n">
-        <v>637</v>
+        <v>288</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>99.70472440944881</v>
+        <v>43.01181102362205</v>
       </c>
     </row>
     <row r="6">
@@ -635,19 +635,19 @@
         <v>5767</v>
       </c>
       <c r="E6" t="n">
-        <v>5643</v>
+        <v>2378</v>
       </c>
       <c r="F6" t="n">
-        <v>1618</v>
+        <v>742</v>
       </c>
       <c r="G6" t="n">
-        <v>3950</v>
+        <v>1568</v>
       </c>
       <c r="H6" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="I6" t="n">
-        <v>97.84983526963759</v>
+        <v>41.23461071614358</v>
       </c>
     </row>
     <row r="7">
@@ -670,19 +670,19 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>2016</v>
+        <v>428</v>
       </c>
       <c r="F7" t="n">
-        <v>776</v>
+        <v>197</v>
       </c>
       <c r="G7" t="n">
-        <v>1242</v>
+        <v>220</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>81.15942028985508</v>
+        <v>17.23027375201288</v>
       </c>
     </row>
     <row r="8">
@@ -705,19 +705,19 @@
         <v>473</v>
       </c>
       <c r="E8" t="n">
-        <v>464</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>333</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>98.09725158562368</v>
+        <v>24.52431289640592</v>
       </c>
     </row>
     <row r="9">
@@ -728,66 +728,66 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OCROS</t>
+          <t>RECUAY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN CRISTOBAL DE RAJAN</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="F9" t="n">
+        <v>88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.4784688995215311</v>
+        <v>74.61538461538461</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RECUAY</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>401</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>99.23076923076923</v>
+        <v>9.725685785536159</v>
       </c>
     </row>
     <row r="11">
@@ -798,31 +798,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>401</v>
+        <v>175</v>
       </c>
       <c r="E11" t="n">
-        <v>397</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>99.00249376558602</v>
+        <v>32.57142857142858</v>
       </c>
     </row>
     <row r="12">
@@ -838,61 +838,61 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>175</v>
+        <v>473</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="F12" t="n">
-        <v>109</v>
+        <v>221</v>
       </c>
       <c r="G12" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>67.65327695560254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>REQUENA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>473</v>
+        <v>392</v>
       </c>
       <c r="E13" t="n">
-        <v>469</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>302</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>99.15433403805497</v>
+        <v>22.19387755102041</v>
       </c>
     </row>
     <row r="14">
@@ -908,61 +908,61 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>392</v>
+        <v>627</v>
       </c>
       <c r="E14" t="n">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>77.55102040816327</v>
+        <v>52.63157894736842</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>REQUENA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>627</v>
+        <v>1492</v>
       </c>
       <c r="E15" t="n">
-        <v>543</v>
+        <v>437</v>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>259</v>
       </c>
       <c r="G15" t="n">
-        <v>466</v>
+        <v>150</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I15" t="n">
-        <v>86.60287081339713</v>
+        <v>29.28954423592493</v>
       </c>
     </row>
     <row r="16">
@@ -973,66 +973,66 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1492</v>
+        <v>7067</v>
       </c>
       <c r="E16" t="n">
-        <v>1421</v>
+        <v>2222</v>
       </c>
       <c r="F16" t="n">
-        <v>964</v>
+        <v>1182</v>
       </c>
       <c r="G16" t="n">
-        <v>258</v>
+        <v>568</v>
       </c>
       <c r="H16" t="n">
-        <v>199</v>
+        <v>479</v>
       </c>
       <c r="I16" t="n">
-        <v>95.24128686327077</v>
+        <v>31.44191311730579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>SATIPO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7067</v>
+        <v>1401</v>
       </c>
       <c r="E17" t="n">
-        <v>5801</v>
+        <v>567</v>
       </c>
       <c r="F17" t="n">
-        <v>2738</v>
+        <v>437</v>
       </c>
       <c r="G17" t="n">
-        <v>1363</v>
+        <v>130</v>
       </c>
       <c r="H17" t="n">
-        <v>1714</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>82.0857506721381</v>
+        <v>40.4710920770878</v>
       </c>
     </row>
     <row r="18">
@@ -1043,66 +1043,66 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>YAULI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1401</v>
+        <v>544</v>
       </c>
       <c r="E18" t="n">
-        <v>1343</v>
+        <v>239</v>
       </c>
       <c r="F18" t="n">
-        <v>1070</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
-        <v>271</v>
+        <v>50</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I18" t="n">
-        <v>95.86009992862242</v>
+        <v>43.93382352941176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YAULI</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="E19" t="n">
-        <v>505</v>
+        <v>159</v>
       </c>
       <c r="F19" t="n">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>199</v>
+        <v>92</v>
       </c>
       <c r="H19" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>92.83088235294117</v>
+        <v>30.34351145038168</v>
       </c>
     </row>
     <row r="20">
@@ -1118,131 +1118,131 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>524</v>
+        <v>161</v>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>33</v>
       </c>
       <c r="F20" t="n">
-        <v>278</v>
+        <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>97.32824427480917</v>
+        <v>20.49689440993789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>161</v>
+        <v>807</v>
       </c>
       <c r="E21" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H21" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>100</v>
+        <v>17.47211895910781</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>TARATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>807</v>
+        <v>515</v>
       </c>
       <c r="E22" t="n">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="F22" t="n">
-        <v>211</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I22" t="n">
-        <v>32.83767038413878</v>
+        <v>41.35922330097087</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TARATA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>515</v>
+        <v>1051</v>
       </c>
       <c r="E23" t="n">
-        <v>512</v>
+        <v>367</v>
       </c>
       <c r="F23" t="n">
         <v>147</v>
       </c>
       <c r="G23" t="n">
-        <v>321</v>
+        <v>197</v>
       </c>
       <c r="H23" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I23" t="n">
-        <v>99.41747572815534</v>
+        <v>34.91912464319695</v>
       </c>
     </row>
     <row r="24">
@@ -1253,31 +1253,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1051</v>
+        <v>2404</v>
       </c>
       <c r="E24" t="n">
-        <v>976</v>
+        <v>1174</v>
       </c>
       <c r="F24" t="n">
-        <v>379</v>
+        <v>884</v>
       </c>
       <c r="G24" t="n">
-        <v>573</v>
+        <v>276</v>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I24" t="n">
-        <v>92.8639391056137</v>
+        <v>48.83527454242929</v>
       </c>
     </row>
     <row r="25">
@@ -1288,31 +1288,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LEONCIO PRADO</t>
+          <t>MARAÑON</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2404</v>
+        <v>761</v>
       </c>
       <c r="E25" t="n">
-        <v>2314</v>
+        <v>289</v>
       </c>
       <c r="F25" t="n">
-        <v>1665</v>
+        <v>246</v>
       </c>
       <c r="G25" t="n">
-        <v>561</v>
+        <v>42</v>
       </c>
       <c r="H25" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>96.25623960066557</v>
+        <v>37.97634691195795</v>
       </c>
     </row>
     <row r="26">
@@ -1328,26 +1328,26 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>761</v>
+        <v>841</v>
       </c>
       <c r="E26" t="n">
-        <v>746</v>
+        <v>97</v>
       </c>
       <c r="F26" t="n">
-        <v>650</v>
+        <v>73</v>
       </c>
       <c r="G26" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>98.02890932982918</v>
+        <v>11.53388822829964</v>
       </c>
     </row>
     <row r="27">
@@ -1358,31 +1358,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MARAÑON</t>
+          <t>YAROWILCA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>841</v>
+        <v>1019</v>
       </c>
       <c r="E27" t="n">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="F27" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>32.81807372175981</v>
+        <v>25.61334641805692</v>
       </c>
     </row>
     <row r="28">
@@ -1398,26 +1398,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1019</v>
+        <v>1251</v>
       </c>
       <c r="E28" t="n">
-        <v>549</v>
+        <v>407</v>
       </c>
       <c r="F28" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="G28" t="n">
-        <v>445</v>
+        <v>287</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>53.87634936211973</v>
+        <v>32.53397282174261</v>
       </c>
     </row>
     <row r="29">
@@ -1433,61 +1433,61 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1251</v>
+        <v>728</v>
       </c>
       <c r="E29" t="n">
-        <v>1149</v>
+        <v>324</v>
       </c>
       <c r="F29" t="n">
-        <v>264</v>
+        <v>152</v>
       </c>
       <c r="G29" t="n">
-        <v>885</v>
+        <v>166</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>91.84652278177458</v>
+        <v>44.5054945054945</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YAROWILCA</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>728</v>
+        <v>525</v>
       </c>
       <c r="E30" t="n">
-        <v>725</v>
+        <v>318</v>
       </c>
       <c r="F30" t="n">
-        <v>427</v>
+        <v>163</v>
       </c>
       <c r="G30" t="n">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
-        <v>99.58791208791209</v>
+        <v>60.57142857142858</v>
       </c>
     </row>
     <row r="31">
@@ -1503,96 +1503,96 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>525</v>
+        <v>236</v>
       </c>
       <c r="E31" t="n">
-        <v>512</v>
+        <v>55</v>
       </c>
       <c r="F31" t="n">
-        <v>295</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>97.52380952380952</v>
+        <v>23.30508474576271</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>TOCACHE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>236</v>
+        <v>734</v>
       </c>
       <c r="E32" t="n">
-        <v>234</v>
+        <v>376</v>
       </c>
       <c r="F32" t="n">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="G32" t="n">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>99.15254237288136</v>
+        <v>51.22615803814714</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TOCACHE</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>734</v>
+        <v>230</v>
       </c>
       <c r="E33" t="n">
-        <v>734</v>
+        <v>172</v>
       </c>
       <c r="F33" t="n">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="G33" t="n">
-        <v>524</v>
+        <v>72</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>100</v>
+        <v>74.78260869565217</v>
       </c>
     </row>
     <row r="34">
@@ -1608,26 +1608,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E34" t="n">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="F34" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="G34" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>74.78260869565217</v>
+        <v>31.30081300813008</v>
       </c>
     </row>
     <row r="35">
@@ -1643,26 +1643,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="E35" t="n">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="F35" t="n">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="G35" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>93.4959349593496</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
@@ -1678,131 +1678,131 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="E36" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F36" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>180</v>
+        <v>1902</v>
       </c>
       <c r="E37" t="n">
-        <v>180</v>
+        <v>622</v>
       </c>
       <c r="F37" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="G37" t="n">
-        <v>106</v>
+        <v>459</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>100</v>
+        <v>32.70241850683491</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1902</v>
+        <v>241</v>
       </c>
       <c r="E38" t="n">
-        <v>1861</v>
+        <v>119</v>
       </c>
       <c r="F38" t="n">
-        <v>547</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>1302</v>
+        <v>116</v>
       </c>
       <c r="H38" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>97.84437434279705</v>
+        <v>49.37759336099585</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>241</v>
+        <v>1075</v>
       </c>
       <c r="E39" t="n">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="G39" t="n">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>99.5850622406639</v>
+        <v>25.48837209302325</v>
       </c>
     </row>
     <row r="40">
@@ -1818,26 +1818,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1075</v>
+        <v>990</v>
       </c>
       <c r="E40" t="n">
-        <v>830</v>
+        <v>515</v>
       </c>
       <c r="F40" t="n">
-        <v>482</v>
+        <v>317</v>
       </c>
       <c r="G40" t="n">
-        <v>247</v>
+        <v>174</v>
       </c>
       <c r="H40" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="I40" t="n">
-        <v>77.20930232558139</v>
+        <v>52.02020202020202</v>
       </c>
     </row>
     <row r="41">
@@ -1853,26 +1853,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>990</v>
+        <v>2150</v>
       </c>
       <c r="E41" t="n">
-        <v>977</v>
+        <v>448</v>
       </c>
       <c r="F41" t="n">
-        <v>599</v>
+        <v>183</v>
       </c>
       <c r="G41" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="H41" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I41" t="n">
-        <v>98.68686868686869</v>
+        <v>20.83720930232558</v>
       </c>
     </row>
     <row r="42">
@@ -1883,31 +1883,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAMANA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2150</v>
+        <v>1644</v>
       </c>
       <c r="E42" t="n">
-        <v>1854</v>
+        <v>704</v>
       </c>
       <c r="F42" t="n">
-        <v>621</v>
+        <v>474</v>
       </c>
       <c r="G42" t="n">
-        <v>1108</v>
+        <v>108</v>
       </c>
       <c r="H42" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I42" t="n">
-        <v>86.23255813953489</v>
+        <v>42.82238442822384</v>
       </c>
     </row>
     <row r="43">
@@ -1918,66 +1918,66 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CAMANA</t>
+          <t>CARAVELI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1644</v>
+        <v>728</v>
       </c>
       <c r="E43" t="n">
-        <v>1587</v>
+        <v>359</v>
       </c>
       <c r="F43" t="n">
-        <v>1009</v>
+        <v>284</v>
       </c>
       <c r="G43" t="n">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="H43" t="n">
-        <v>379</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>96.53284671532847</v>
+        <v>49.31318681318682</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CARAVELI</t>
+          <t>LUCANAS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="E44" t="n">
-        <v>726</v>
+        <v>252</v>
       </c>
       <c r="F44" t="n">
-        <v>556</v>
+        <v>142</v>
       </c>
       <c r="G44" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H44" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>99.72527472527473</v>
+        <v>36.2589928057554</v>
       </c>
     </row>
     <row r="45">
@@ -1988,31 +1988,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LUCANAS</t>
+          <t>PAUCAR DEL SARA SARA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>695</v>
+        <v>355</v>
       </c>
       <c r="E45" t="n">
-        <v>595</v>
+        <v>222</v>
       </c>
       <c r="F45" t="n">
-        <v>355</v>
+        <v>175</v>
       </c>
       <c r="G45" t="n">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="H45" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>85.61151079136691</v>
+        <v>62.53521126760564</v>
       </c>
     </row>
     <row r="46">
@@ -2023,171 +2023,171 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PAUCAR DEL SARA SARA</t>
+          <t>VICTOR FAJARDO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>355</v>
+        <v>727</v>
       </c>
       <c r="E46" t="n">
-        <v>298</v>
+        <v>367</v>
       </c>
       <c r="F46" t="n">
-        <v>243</v>
+        <v>94</v>
       </c>
       <c r="G46" t="n">
-        <v>52</v>
+        <v>258</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I46" t="n">
-        <v>83.94366197183099</v>
+        <v>50.48143053645116</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>727</v>
+        <v>1667</v>
       </c>
       <c r="E47" t="n">
-        <v>726</v>
+        <v>839</v>
       </c>
       <c r="F47" t="n">
-        <v>257</v>
+        <v>527</v>
       </c>
       <c r="G47" t="n">
-        <v>394</v>
+        <v>142</v>
       </c>
       <c r="H47" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>99.86244841815682</v>
+        <v>50.32993401319737</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>SANDIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1667</v>
+        <v>1350</v>
       </c>
       <c r="E48" t="n">
-        <v>1638</v>
+        <v>390</v>
       </c>
       <c r="F48" t="n">
-        <v>1133</v>
+        <v>210</v>
       </c>
       <c r="G48" t="n">
-        <v>314</v>
+        <v>125</v>
       </c>
       <c r="H48" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="I48" t="n">
-        <v>98.26034793041391</v>
+        <v>28.88888888888889</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANDIA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1350</v>
+        <v>1082</v>
       </c>
       <c r="E49" t="n">
-        <v>1274</v>
+        <v>153</v>
       </c>
       <c r="F49" t="n">
-        <v>870</v>
+        <v>102</v>
       </c>
       <c r="G49" t="n">
-        <v>264</v>
+        <v>31</v>
       </c>
       <c r="H49" t="n">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>94.37037037037037</v>
+        <v>14.14048059149723</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1082</v>
+        <v>320</v>
       </c>
       <c r="E50" t="n">
-        <v>833</v>
+        <v>237</v>
       </c>
       <c r="F50" t="n">
-        <v>487</v>
+        <v>135</v>
       </c>
       <c r="G50" t="n">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="H50" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>76.98706099815156</v>
+        <v>74.0625</v>
       </c>
     </row>
     <row r="51">
@@ -2203,96 +2203,61 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>320</v>
+        <v>271</v>
       </c>
       <c r="E51" t="n">
-        <v>305</v>
+        <v>46</v>
       </c>
       <c r="F51" t="n">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="G51" t="n">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>95.3125</v>
+        <v>16.97416974169742</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>CHACHAPOYAS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>271</v>
+        <v>109</v>
       </c>
       <c r="E52" t="n">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="F52" t="n">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>99.63099630996311</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>SONCHE</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>109</v>
-      </c>
-      <c r="E53" t="n">
-        <v>109</v>
-      </c>
-      <c r="F53" t="n">
-        <v>29</v>
-      </c>
-      <c r="G53" t="n">
-        <v>80</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>100</v>
+        <v>50.45871559633027</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,19 +495,19 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>4525</v>
+        <v>11435</v>
       </c>
       <c r="F2" t="n">
-        <v>1067</v>
+        <v>3409</v>
       </c>
       <c r="G2" t="n">
-        <v>3236</v>
+        <v>7574</v>
       </c>
       <c r="H2" t="n">
-        <v>215</v>
+        <v>455</v>
       </c>
       <c r="I2" t="n">
-        <v>36.74679226896216</v>
+        <v>92.86178333604028</v>
       </c>
     </row>
     <row r="3">
@@ -530,19 +530,19 @@
         <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>45.76271186440678</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>160</v>
       </c>
       <c r="E4" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H4" t="n">
         <v>48</v>
       </c>
       <c r="I4" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -600,19 +600,19 @@
         <v>1016</v>
       </c>
       <c r="E5" t="n">
-        <v>437</v>
+        <v>1013</v>
       </c>
       <c r="F5" t="n">
-        <v>148</v>
+        <v>377</v>
       </c>
       <c r="G5" t="n">
-        <v>288</v>
+        <v>637</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>43.01181102362205</v>
+        <v>99.70472440944881</v>
       </c>
     </row>
     <row r="6">
@@ -635,19 +635,19 @@
         <v>5767</v>
       </c>
       <c r="E6" t="n">
-        <v>2378</v>
+        <v>5643</v>
       </c>
       <c r="F6" t="n">
-        <v>742</v>
+        <v>1618</v>
       </c>
       <c r="G6" t="n">
-        <v>1568</v>
+        <v>3950</v>
       </c>
       <c r="H6" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I6" t="n">
-        <v>41.23461071614358</v>
+        <v>97.84983526963759</v>
       </c>
     </row>
     <row r="7">
@@ -670,19 +670,19 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>428</v>
+        <v>2265</v>
       </c>
       <c r="F7" t="n">
-        <v>197</v>
+        <v>859</v>
       </c>
       <c r="G7" t="n">
-        <v>220</v>
+        <v>1407</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>17.23027375201288</v>
+        <v>91.18357487922705</v>
       </c>
     </row>
     <row r="8">
@@ -705,19 +705,19 @@
         <v>473</v>
       </c>
       <c r="E8" t="n">
+        <v>464</v>
+      </c>
+      <c r="F8" t="n">
+        <v>333</v>
+      </c>
+      <c r="G8" t="n">
         <v>116</v>
       </c>
-      <c r="F8" t="n">
-        <v>64</v>
-      </c>
-      <c r="G8" t="n">
-        <v>50</v>
-      </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>24.52431289640592</v>
+        <v>98.09725158562368</v>
       </c>
     </row>
     <row r="9">
@@ -728,101 +728,101 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RECUAY</t>
+          <t>OCROS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>SAN CRISTOBAL DE RAJAN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>74.61538461538461</v>
+        <v>9.569377990430622</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>OCROS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>401</v>
+        <v>192</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>9.725685785536159</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>RECUAY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>32.57142857142858</v>
+        <v>99.23076923076923</v>
       </c>
     </row>
     <row r="12">
@@ -833,451 +833,451 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="E12" t="n">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="F12" t="n">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="G12" t="n">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>67.65327695560254</v>
+        <v>99.00249376558602</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REQUENA</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>392</v>
+        <v>175</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>22.19387755102041</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REQUENA</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>627</v>
+        <v>473</v>
       </c>
       <c r="E14" t="n">
-        <v>330</v>
+        <v>469</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>302</v>
       </c>
       <c r="G14" t="n">
-        <v>266</v>
+        <v>166</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>52.63157894736842</v>
+        <v>99.15433403805497</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>REQUENA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1492</v>
+        <v>392</v>
       </c>
       <c r="E15" t="n">
-        <v>437</v>
+        <v>392</v>
       </c>
       <c r="F15" t="n">
-        <v>259</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>150</v>
+        <v>317</v>
       </c>
       <c r="H15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>29.28954423592493</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>REQUENA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7067</v>
+        <v>627</v>
       </c>
       <c r="E16" t="n">
-        <v>2222</v>
+        <v>543</v>
       </c>
       <c r="F16" t="n">
-        <v>1182</v>
+        <v>75</v>
       </c>
       <c r="G16" t="n">
-        <v>568</v>
+        <v>466</v>
       </c>
       <c r="H16" t="n">
-        <v>479</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>31.44191311730579</v>
+        <v>86.60287081339713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SATIPO</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1401</v>
+        <v>1492</v>
       </c>
       <c r="E17" t="n">
-        <v>567</v>
+        <v>1422</v>
       </c>
       <c r="F17" t="n">
-        <v>437</v>
+        <v>965</v>
       </c>
       <c r="G17" t="n">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="I17" t="n">
-        <v>40.4710920770878</v>
+        <v>95.3083109919571</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YAULI</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>544</v>
+        <v>7067</v>
       </c>
       <c r="E18" t="n">
-        <v>239</v>
+        <v>6001</v>
       </c>
       <c r="F18" t="n">
-        <v>130</v>
+        <v>2777</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>1394</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>1851</v>
       </c>
       <c r="I18" t="n">
-        <v>43.93382352941176</v>
+        <v>84.91580585821423</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>SATIPO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>524</v>
+        <v>1401</v>
       </c>
       <c r="E19" t="n">
-        <v>159</v>
+        <v>1343</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>1070</v>
       </c>
       <c r="G19" t="n">
-        <v>92</v>
+        <v>271</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>30.34351145038168</v>
+        <v>95.86009992862242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>YAULI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>161</v>
+        <v>544</v>
       </c>
       <c r="E20" t="n">
-        <v>33</v>
+        <v>505</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="I20" t="n">
-        <v>20.49689440993789</v>
+        <v>92.83088235294117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>807</v>
+        <v>524</v>
       </c>
       <c r="E21" t="n">
-        <v>141</v>
+        <v>510</v>
       </c>
       <c r="F21" t="n">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="G21" t="n">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>17.47211895910781</v>
+        <v>97.32824427480917</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TARATA</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>515</v>
+        <v>161</v>
       </c>
       <c r="E22" t="n">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G22" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="I22" t="n">
-        <v>41.35922330097087</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1051</v>
+        <v>807</v>
       </c>
       <c r="E23" t="n">
-        <v>367</v>
+        <v>283</v>
       </c>
       <c r="F23" t="n">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="G23" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="H23" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>34.91912464319695</v>
+        <v>35.06815365551425</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LEONCIO PRADO</t>
+          <t>TARATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2404</v>
+        <v>515</v>
       </c>
       <c r="E24" t="n">
-        <v>1174</v>
+        <v>512</v>
       </c>
       <c r="F24" t="n">
-        <v>884</v>
+        <v>147</v>
       </c>
       <c r="G24" t="n">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="H24" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="I24" t="n">
-        <v>48.83527454242929</v>
+        <v>99.41747572815534</v>
       </c>
     </row>
     <row r="25">
@@ -1288,31 +1288,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MARAÑON</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>761</v>
+        <v>1051</v>
       </c>
       <c r="E25" t="n">
-        <v>289</v>
+        <v>1012</v>
       </c>
       <c r="F25" t="n">
-        <v>246</v>
+        <v>385</v>
       </c>
       <c r="G25" t="n">
-        <v>42</v>
+        <v>603</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I25" t="n">
-        <v>37.97634691195795</v>
+        <v>96.28924833491912</v>
       </c>
     </row>
     <row r="26">
@@ -1323,31 +1323,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MARAÑON</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>841</v>
+        <v>2404</v>
       </c>
       <c r="E26" t="n">
-        <v>97</v>
+        <v>2326</v>
       </c>
       <c r="F26" t="n">
-        <v>73</v>
+        <v>1672</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>566</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I26" t="n">
-        <v>11.53388822829964</v>
+        <v>96.75540765391015</v>
       </c>
     </row>
     <row r="27">
@@ -1358,31 +1358,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YAROWILCA</t>
+          <t>MARAÑON</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1019</v>
+        <v>761</v>
       </c>
       <c r="E27" t="n">
-        <v>261</v>
+        <v>746</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="G27" t="n">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I27" t="n">
-        <v>25.61334641805692</v>
+        <v>98.02890932982918</v>
       </c>
     </row>
     <row r="28">
@@ -1393,31 +1393,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YAROWILCA</t>
+          <t>MARAÑON</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1251</v>
+        <v>841</v>
       </c>
       <c r="E28" t="n">
-        <v>407</v>
+        <v>316</v>
       </c>
       <c r="F28" t="n">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="G28" t="n">
-        <v>287</v>
+        <v>92</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>32.53397282174261</v>
+        <v>37.5743162901308</v>
       </c>
     </row>
     <row r="29">
@@ -1433,201 +1433,201 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>728</v>
+        <v>1019</v>
       </c>
       <c r="E29" t="n">
-        <v>324</v>
+        <v>549</v>
       </c>
       <c r="F29" t="n">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="G29" t="n">
-        <v>166</v>
+        <v>445</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>44.5054945054945</v>
+        <v>53.87634936211973</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>YAROWILCA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>525</v>
+        <v>1251</v>
       </c>
       <c r="E30" t="n">
-        <v>318</v>
+        <v>1171</v>
       </c>
       <c r="F30" t="n">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="G30" t="n">
-        <v>143</v>
+        <v>900</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>60.57142857142858</v>
+        <v>93.60511590727418</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>YAROWILCA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>236</v>
+        <v>728</v>
       </c>
       <c r="E31" t="n">
-        <v>55</v>
+        <v>725</v>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>427</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>291</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
-        <v>23.30508474576271</v>
+        <v>99.58791208791209</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TOCACHE</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>734</v>
+        <v>525</v>
       </c>
       <c r="E32" t="n">
-        <v>376</v>
+        <v>512</v>
       </c>
       <c r="F32" t="n">
-        <v>122</v>
+        <v>295</v>
       </c>
       <c r="G32" t="n">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>51.22615803814714</v>
+        <v>97.52380952380952</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E33" t="n">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="F33" t="n">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="G33" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>74.78260869565217</v>
+        <v>99.15254237288136</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TOCACHE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>246</v>
+        <v>734</v>
       </c>
       <c r="E34" t="n">
-        <v>77</v>
+        <v>734</v>
       </c>
       <c r="F34" t="n">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>524</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>31.30081300813008</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -1643,26 +1643,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="E35" t="n">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="G35" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>74.78260869565217</v>
       </c>
     </row>
     <row r="36">
@@ -1678,61 +1678,61 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="E36" t="n">
-        <v>45</v>
+        <v>230</v>
       </c>
       <c r="F36" t="n">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="G36" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>93.4959349593496</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1902</v>
+        <v>74</v>
       </c>
       <c r="E37" t="n">
-        <v>622</v>
+        <v>74</v>
       </c>
       <c r="F37" t="n">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="G37" t="n">
-        <v>459</v>
+        <v>22</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>32.70241850683491</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -1748,96 +1748,96 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="E38" t="n">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G38" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>49.37759336099585</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1075</v>
+        <v>1902</v>
       </c>
       <c r="E39" t="n">
-        <v>274</v>
+        <v>1863</v>
       </c>
       <c r="F39" t="n">
-        <v>200</v>
+        <v>547</v>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>1304</v>
       </c>
       <c r="H39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I39" t="n">
-        <v>25.48837209302325</v>
+        <v>97.94952681388013</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>990</v>
+        <v>241</v>
       </c>
       <c r="E40" t="n">
-        <v>515</v>
+        <v>240</v>
       </c>
       <c r="F40" t="n">
-        <v>317</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="H40" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>52.02020202020202</v>
+        <v>99.5850622406639</v>
       </c>
     </row>
     <row r="41">
@@ -1853,26 +1853,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2150</v>
+        <v>1075</v>
       </c>
       <c r="E41" t="n">
-        <v>448</v>
+        <v>867</v>
       </c>
       <c r="F41" t="n">
-        <v>183</v>
+        <v>515</v>
       </c>
       <c r="G41" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H41" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="I41" t="n">
-        <v>20.83720930232558</v>
+        <v>80.65116279069767</v>
       </c>
     </row>
     <row r="42">
@@ -1883,31 +1883,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAMANA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1644</v>
+        <v>990</v>
       </c>
       <c r="E42" t="n">
-        <v>704</v>
+        <v>977</v>
       </c>
       <c r="F42" t="n">
-        <v>474</v>
+        <v>599</v>
       </c>
       <c r="G42" t="n">
-        <v>108</v>
+        <v>307</v>
       </c>
       <c r="H42" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="I42" t="n">
-        <v>42.82238442822384</v>
+        <v>98.68686868686869</v>
       </c>
     </row>
     <row r="43">
@@ -1918,101 +1918,101 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CARAVELI</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>728</v>
+        <v>2150</v>
       </c>
       <c r="E43" t="n">
-        <v>359</v>
+        <v>2062</v>
       </c>
       <c r="F43" t="n">
-        <v>284</v>
+        <v>649</v>
       </c>
       <c r="G43" t="n">
-        <v>66</v>
+        <v>1281</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="I43" t="n">
-        <v>49.31318681318682</v>
+        <v>95.90697674418604</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LUCANAS</t>
+          <t>CAMANA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>695</v>
+        <v>1644</v>
       </c>
       <c r="E44" t="n">
-        <v>252</v>
+        <v>1633</v>
       </c>
       <c r="F44" t="n">
-        <v>142</v>
+        <v>1026</v>
       </c>
       <c r="G44" t="n">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>405</v>
       </c>
       <c r="I44" t="n">
-        <v>36.2589928057554</v>
+        <v>99.330900243309</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PAUCAR DEL SARA SARA</t>
+          <t>CARAVELI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>355</v>
+        <v>728</v>
       </c>
       <c r="E45" t="n">
-        <v>222</v>
+        <v>726</v>
       </c>
       <c r="F45" t="n">
-        <v>175</v>
+        <v>556</v>
       </c>
       <c r="G45" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="I45" t="n">
-        <v>62.53521126760564</v>
+        <v>99.72527472527473</v>
       </c>
     </row>
     <row r="46">
@@ -2023,241 +2023,311 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO</t>
+          <t>LUCANAS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>727</v>
+        <v>695</v>
       </c>
       <c r="E46" t="n">
-        <v>367</v>
+        <v>595</v>
       </c>
       <c r="F46" t="n">
-        <v>94</v>
+        <v>355</v>
       </c>
       <c r="G46" t="n">
-        <v>258</v>
+        <v>185</v>
       </c>
       <c r="H46" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="I46" t="n">
-        <v>50.48143053645116</v>
+        <v>85.61151079136691</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>PAUCAR DEL SARA SARA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1667</v>
+        <v>355</v>
       </c>
       <c r="E47" t="n">
-        <v>839</v>
+        <v>329</v>
       </c>
       <c r="F47" t="n">
-        <v>527</v>
+        <v>274</v>
       </c>
       <c r="G47" t="n">
-        <v>142</v>
+        <v>52</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>50.32993401319737</v>
+        <v>92.67605633802816</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANDIA</t>
+          <t>VICTOR FAJARDO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1350</v>
+        <v>727</v>
       </c>
       <c r="E48" t="n">
-        <v>390</v>
+        <v>726</v>
       </c>
       <c r="F48" t="n">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="G48" t="n">
-        <v>125</v>
+        <v>394</v>
       </c>
       <c r="H48" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="I48" t="n">
-        <v>28.88888888888889</v>
+        <v>99.86244841815682</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1082</v>
+        <v>1667</v>
       </c>
       <c r="E49" t="n">
-        <v>153</v>
+        <v>1638</v>
       </c>
       <c r="F49" t="n">
-        <v>102</v>
+        <v>1133</v>
       </c>
       <c r="G49" t="n">
-        <v>31</v>
+        <v>314</v>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I49" t="n">
-        <v>14.14048059149723</v>
+        <v>98.26034793041391</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>SANDIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>320</v>
+        <v>1350</v>
       </c>
       <c r="E50" t="n">
-        <v>237</v>
+        <v>1274</v>
       </c>
       <c r="F50" t="n">
-        <v>135</v>
+        <v>870</v>
       </c>
       <c r="G50" t="n">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="I50" t="n">
-        <v>74.0625</v>
+        <v>94.37037037037037</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YAUYOS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>271</v>
+        <v>1082</v>
       </c>
       <c r="E51" t="n">
-        <v>46</v>
+        <v>979</v>
       </c>
       <c r="F51" t="n">
-        <v>17</v>
+        <v>556</v>
       </c>
       <c r="G51" t="n">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="I51" t="n">
-        <v>16.97416974169742</v>
+        <v>90.48059149722735</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHACHAPOYAS</t>
+          <t>YAUYOS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="E52" t="n">
-        <v>55</v>
+        <v>305</v>
       </c>
       <c r="F52" t="n">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="G52" t="n">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>50.45871559633027</v>
+        <v>95.3125</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>YAUYOS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AZANGARO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>271</v>
+      </c>
+      <c r="E53" t="n">
+        <v>270</v>
+      </c>
+      <c r="F53" t="n">
+        <v>86</v>
+      </c>
+      <c r="G53" t="n">
+        <v>184</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>99.63099630996311</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SONCHE</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>109</v>
+      </c>
+      <c r="E54" t="n">
+        <v>109</v>
+      </c>
+      <c r="F54" t="n">
+        <v>29</v>
+      </c>
+      <c r="G54" t="n">
+        <v>80</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_distrito.xlsx
+++ b/data/tabla_desagregada_distrito.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>tipo_sin_causal</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>PORC_AVANCE</t>
         </is>
       </c>
@@ -495,19 +500,22 @@
         <v>12314</v>
       </c>
       <c r="E2" t="n">
-        <v>11435</v>
+        <v>11546</v>
       </c>
       <c r="F2" t="n">
-        <v>3409</v>
+        <v>3466</v>
       </c>
       <c r="G2" t="n">
-        <v>7574</v>
+        <v>7627</v>
       </c>
       <c r="H2" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I2" t="n">
-        <v>92.86178333604028</v>
+        <v>25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>93.76319636186454</v>
       </c>
     </row>
     <row r="3">
@@ -542,6 +550,9 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -577,6 +588,9 @@
         <v>48</v>
       </c>
       <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>100</v>
       </c>
     </row>
@@ -612,6 +626,9 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>99.70472440944881</v>
       </c>
     </row>
@@ -647,6 +664,9 @@
         <v>71</v>
       </c>
       <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
         <v>97.84983526963759</v>
       </c>
     </row>
@@ -670,19 +690,22 @@
         <v>2484</v>
       </c>
       <c r="E7" t="n">
-        <v>2265</v>
+        <v>2287</v>
       </c>
       <c r="F7" t="n">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="G7" t="n">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="H7" t="n">
         <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>91.18357487922705</v>
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>92.06924315619968</v>
       </c>
     </row>
     <row r="8">
@@ -717,6 +740,9 @@
         <v>12</v>
       </c>
       <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
         <v>98.09725158562368</v>
       </c>
     </row>
@@ -740,19 +766,22 @@
         <v>209</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="I9" t="n">
-        <v>9.569377990430622</v>
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>54.06698564593302</v>
       </c>
     </row>
     <row r="10">
@@ -775,19 +804,22 @@
         <v>192</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>34.375</v>
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>97.91666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -822,6 +854,9 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>99.23076923076923</v>
       </c>
     </row>
@@ -857,6 +892,9 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>99.00249376558602</v>
       </c>
     </row>
@@ -892,6 +930,9 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>100</v>
       </c>
     </row>
@@ -927,6 +968,9 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>99.15433403805497</v>
       </c>
     </row>
@@ -962,6 +1006,9 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>100</v>
       </c>
     </row>
@@ -997,6 +1044,9 @@
         <v>3</v>
       </c>
       <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
         <v>86.60287081339713</v>
       </c>
     </row>
@@ -1032,6 +1082,9 @@
         <v>199</v>
       </c>
       <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
         <v>95.3083109919571</v>
       </c>
     </row>
@@ -1055,19 +1108,22 @@
         <v>7067</v>
       </c>
       <c r="E18" t="n">
-        <v>6001</v>
+        <v>6080</v>
       </c>
       <c r="F18" t="n">
-        <v>2777</v>
+        <v>2826</v>
       </c>
       <c r="G18" t="n">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="H18" t="n">
-        <v>1851</v>
+        <v>1873</v>
       </c>
       <c r="I18" t="n">
-        <v>84.91580585821423</v>
+        <v>22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>86.0336776567143</v>
       </c>
     </row>
     <row r="19">
@@ -1102,6 +1158,9 @@
         <v>6</v>
       </c>
       <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>95.86009992862242</v>
       </c>
     </row>
@@ -1137,6 +1196,9 @@
         <v>136</v>
       </c>
       <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
         <v>92.83088235294117</v>
       </c>
     </row>
@@ -1172,6 +1234,9 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" t="n">
         <v>97.32824427480917</v>
       </c>
     </row>
@@ -1207,6 +1272,9 @@
         <v>92</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1230,19 +1298,22 @@
         <v>807</v>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>402</v>
       </c>
       <c r="F23" t="n">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="H23" t="n">
         <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>35.06815365551425</v>
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>49.81412639405205</v>
       </c>
     </row>
     <row r="24">
@@ -1277,6 +1348,9 @@
         <v>43</v>
       </c>
       <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
         <v>99.41747572815534</v>
       </c>
     </row>
@@ -1312,6 +1386,9 @@
         <v>24</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>96.28924833491912</v>
       </c>
     </row>
@@ -1335,19 +1412,22 @@
         <v>2404</v>
       </c>
       <c r="E26" t="n">
-        <v>2326</v>
+        <v>2396</v>
       </c>
       <c r="F26" t="n">
-        <v>1672</v>
+        <v>1736</v>
       </c>
       <c r="G26" t="n">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="H26" t="n">
         <v>86</v>
       </c>
       <c r="I26" t="n">
-        <v>96.75540765391015</v>
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>99.66722129783693</v>
       </c>
     </row>
     <row r="27">
@@ -1382,6 +1462,9 @@
         <v>15</v>
       </c>
       <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
         <v>98.02890932982918</v>
       </c>
     </row>
@@ -1405,19 +1488,22 @@
         <v>841</v>
       </c>
       <c r="E28" t="n">
-        <v>316</v>
+        <v>417</v>
       </c>
       <c r="F28" t="n">
-        <v>224</v>
+        <v>318</v>
       </c>
       <c r="G28" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>37.5743162901308</v>
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>49.58382877526754</v>
       </c>
     </row>
     <row r="29">
@@ -1452,6 +1538,9 @@
         <v>5</v>
       </c>
       <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
         <v>53.87634936211973</v>
       </c>
     </row>
@@ -1487,6 +1576,9 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
         <v>93.60511590727418</v>
       </c>
     </row>
@@ -1522,6 +1614,9 @@
         <v>8</v>
       </c>
       <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
         <v>99.58791208791209</v>
       </c>
     </row>
@@ -1557,6 +1652,9 @@
         <v>13</v>
       </c>
       <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>97.52380952380952</v>
       </c>
     </row>
@@ -1592,6 +1690,9 @@
         <v>2</v>
       </c>
       <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>99.15254237288136</v>
       </c>
     </row>
@@ -1627,6 +1728,9 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1662,6 +1766,9 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
         <v>74.78260869565217</v>
       </c>
     </row>
@@ -1685,19 +1792,22 @@
         <v>246</v>
       </c>
       <c r="E36" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="F36" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G36" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>93.4959349593496</v>
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>99.1869918699187</v>
       </c>
     </row>
     <row r="37">
@@ -1732,6 +1842,9 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1767,6 +1880,9 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1802,6 +1918,9 @@
         <v>18</v>
       </c>
       <c r="I39" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" t="n">
         <v>97.94952681388013</v>
       </c>
     </row>
@@ -1837,6 +1956,9 @@
         <v>2</v>
       </c>
       <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>99.5850622406639</v>
       </c>
     </row>
@@ -1872,6 +1994,9 @@
         <v>101</v>
       </c>
       <c r="I41" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" t="n">
         <v>80.65116279069767</v>
       </c>
     </row>
@@ -1907,6 +2032,9 @@
         <v>60</v>
       </c>
       <c r="I42" t="n">
+        <v>18</v>
+      </c>
+      <c r="J42" t="n">
         <v>98.68686868686869</v>
       </c>
     </row>
@@ -1930,19 +2058,22 @@
         <v>2150</v>
       </c>
       <c r="E43" t="n">
-        <v>2062</v>
+        <v>2112</v>
       </c>
       <c r="F43" t="n">
         <v>649</v>
       </c>
       <c r="G43" t="n">
-        <v>1281</v>
+        <v>1310</v>
       </c>
       <c r="H43" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="I43" t="n">
-        <v>95.90697674418604</v>
+        <v>11</v>
+      </c>
+      <c r="J43" t="n">
+        <v>98.23255813953489</v>
       </c>
     </row>
     <row r="44">
@@ -1977,6 +2108,9 @@
         <v>405</v>
       </c>
       <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
         <v>99.330900243309</v>
       </c>
     </row>
@@ -2012,6 +2146,9 @@
         <v>73</v>
       </c>
       <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
         <v>99.72527472527473</v>
       </c>
     </row>
@@ -2047,6 +2184,9 @@
         <v>57</v>
       </c>
       <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>85.61151079136691</v>
       </c>
     </row>
@@ -2082,6 +2222,9 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>92.67605633802816</v>
       </c>
     </row>
@@ -2117,6 +2260,9 @@
         <v>73</v>
       </c>
       <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n">
         <v>99.86244841815682</v>
       </c>
     </row>
@@ -2152,6 +2298,9 @@
         <v>22</v>
       </c>
       <c r="I49" t="n">
+        <v>265</v>
+      </c>
+      <c r="J49" t="n">
         <v>98.26034793041391</v>
       </c>
     </row>
@@ -2175,10 +2324,10 @@
         <v>1350</v>
       </c>
       <c r="E50" t="n">
-        <v>1274</v>
+        <v>1345</v>
       </c>
       <c r="F50" t="n">
-        <v>870</v>
+        <v>941</v>
       </c>
       <c r="G50" t="n">
         <v>264</v>
@@ -2187,7 +2336,10 @@
         <v>138</v>
       </c>
       <c r="I50" t="n">
-        <v>94.37037037037037</v>
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>99.62962962962963</v>
       </c>
     </row>
     <row r="51">
@@ -2222,6 +2374,9 @@
         <v>178</v>
       </c>
       <c r="I51" t="n">
+        <v>78</v>
+      </c>
+      <c r="J51" t="n">
         <v>90.48059149722735</v>
       </c>
     </row>
@@ -2257,6 +2412,9 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
         <v>95.3125</v>
       </c>
     </row>
@@ -2292,6 +2450,9 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>99.63099630996311</v>
       </c>
     </row>
@@ -2327,6 +2488,9 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
         <v>100</v>
       </c>
     </row>
